--- a/NFXL.xlsx
+++ b/NFXL.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/silviu/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silva\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9CC112-DA24-3244-912A-8C7F9774FCBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBDB9BF-9479-41B9-89D2-BEC3920BF41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1540" yWindow="800" windowWidth="18640" windowHeight="18660" activeTab="1" xr2:uid="{8021568F-0C01-784D-8C5A-6AF22953FEA0}"/>
+    <workbookView xWindow="5940" yWindow="3720" windowWidth="16065" windowHeight="11880" activeTab="1" xr2:uid="{8021568F-0C01-784D-8C5A-6AF22953FEA0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Main" sheetId="1" r:id="rId1"/>
+    <sheet name="Model" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="98">
   <si>
     <t>Price</t>
   </si>
@@ -313,13 +313,34 @@
   </si>
   <si>
     <t>FCT TTM</t>
+  </si>
+  <si>
+    <t>Terminal</t>
+  </si>
+  <si>
+    <t>ROIC</t>
+  </si>
+  <si>
+    <t>NPV</t>
+  </si>
+  <si>
+    <t>Share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discount </t>
+  </si>
+  <si>
+    <t>Upside</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+  </numFmts>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -366,6 +387,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -384,10 +412,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -412,9 +441,13 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -851,15 +884,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F472637-04C3-D546-B7D5-B73335D0AD99}">
-  <dimension ref="J3:K8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="J3:L8"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="10" width="10.83203125" style="1"/>
-    <col min="11" max="11" width="16.83203125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="10" width="10.875" style="1"/>
+    <col min="11" max="11" width="16.875" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J3" s="1" t="s">
         <v>0</v>
       </c>
@@ -867,15 +900,18 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K4" s="1">
         <v>4222162</v>
       </c>
-    </row>
-    <row r="5" spans="10:11" x14ac:dyDescent="0.2">
+      <c r="L4" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J5" s="1" t="s">
         <v>2</v>
       </c>
@@ -884,31 +920,37 @@
         <v>325106474</v>
       </c>
     </row>
-    <row r="6" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K6" s="1">
-        <f>9287287+37105</f>
-        <v>9324392</v>
-      </c>
-    </row>
-    <row r="7" spans="10:11" x14ac:dyDescent="0.2">
+        <f>9033681+28678</f>
+        <v>9062359</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J7" s="1" t="s">
         <v>4</v>
       </c>
       <c r="K7" s="1">
-        <f>14463020</f>
-        <v>14463020</v>
-      </c>
-    </row>
-    <row r="8" spans="10:11" x14ac:dyDescent="0.2">
+        <f>998865+13463971</f>
+        <v>14462836</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K8" s="1">
         <f>K5+K7-K6</f>
-        <v>330245102</v>
+        <v>330506951</v>
       </c>
     </row>
   </sheetData>
@@ -919,17 +961,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5A6E14F-A8E6-9948-97A9-7680EC20D896}">
   <dimension ref="B1:DJ126"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="2"/>
-    <col min="2" max="2" width="33.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.875" style="2"/>
+    <col min="2" max="2" width="33.875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="21" width="10.83203125" style="2"/>
+    <col min="4" max="21" width="10.875" style="2"/>
     <col min="22" max="22" width="11" style="2" customWidth="1"/>
-    <col min="23" max="16384" width="10.83203125" style="2"/>
+    <col min="23" max="45" width="10.875" style="2"/>
+    <col min="46" max="46" width="14.25" style="2" customWidth="1"/>
+    <col min="47" max="16384" width="10.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:114" ht="14" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:114" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
@@ -1043,7 +1087,7 @@
       <c r="DI1" s="4"/>
       <c r="DJ1" s="4"/>
     </row>
-    <row r="2" spans="2:114" ht="14" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:114" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>19</v>
       </c>
@@ -1285,7 +1329,7 @@
       <c r="DI2" s="4"/>
       <c r="DJ2" s="4"/>
     </row>
-    <row r="3" spans="2:114" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:114" x14ac:dyDescent="0.2">
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
@@ -1348,6 +1392,22 @@
       </c>
       <c r="V3" s="5">
         <v>12050762</v>
+      </c>
+      <c r="W3" s="5">
+        <f>S3*1.1</f>
+        <v>11597081.100000001</v>
+      </c>
+      <c r="X3" s="5">
+        <f t="shared" ref="X3:Z4" si="1">T3*1.1</f>
+        <v>12187082.600000001</v>
+      </c>
+      <c r="Y3" s="5">
+        <f t="shared" si="1"/>
+        <v>12661337.700000001</v>
+      </c>
+      <c r="Z3" s="5">
+        <f t="shared" si="1"/>
+        <v>13255838.200000001</v>
       </c>
       <c r="AC3" s="2">
         <v>2162625</v>
@@ -1401,8 +1461,52 @@
         <f>SUM(S3:V3)</f>
         <v>45183036</v>
       </c>
-    </row>
-    <row r="4" spans="2:114" x14ac:dyDescent="0.15">
+      <c r="AS3" s="2">
+        <f>AR3*1.1</f>
+        <v>49701339.600000001</v>
+      </c>
+      <c r="AT3" s="2">
+        <f t="shared" ref="AT3:BC3" si="2">AS3*1.1</f>
+        <v>54671473.560000002</v>
+      </c>
+      <c r="AU3" s="2">
+        <f t="shared" si="2"/>
+        <v>60138620.916000009</v>
+      </c>
+      <c r="AV3" s="2">
+        <f t="shared" si="2"/>
+        <v>66152483.007600017</v>
+      </c>
+      <c r="AW3" s="2">
+        <f t="shared" si="2"/>
+        <v>72767731.308360025</v>
+      </c>
+      <c r="AX3" s="2">
+        <f t="shared" si="2"/>
+        <v>80044504.439196035</v>
+      </c>
+      <c r="AY3" s="2">
+        <f t="shared" si="2"/>
+        <v>88048954.883115649</v>
+      </c>
+      <c r="AZ3" s="2">
+        <f t="shared" si="2"/>
+        <v>96853850.371427223</v>
+      </c>
+      <c r="BA3" s="2">
+        <f t="shared" si="2"/>
+        <v>106539235.40856995</v>
+      </c>
+      <c r="BB3" s="2">
+        <f t="shared" si="2"/>
+        <v>117193158.94942695</v>
+      </c>
+      <c r="BC3" s="2">
+        <f t="shared" si="2"/>
+        <v>128912474.84436965</v>
+      </c>
+    </row>
+    <row r="4" spans="2:114" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
@@ -1465,6 +1569,22 @@
       </c>
       <c r="V4" s="6">
         <v>6522621</v>
+      </c>
+      <c r="W4" s="6">
+        <f>S4*1.1</f>
+        <v>5789461.7000000002</v>
+      </c>
+      <c r="X4" s="6">
+        <f t="shared" si="1"/>
+        <v>5857842.1000000006</v>
+      </c>
+      <c r="Y4" s="6">
+        <f t="shared" si="1"/>
+        <v>6780675.0000000009</v>
+      </c>
+      <c r="Z4" s="6">
+        <f t="shared" si="1"/>
+        <v>7174883.1000000006</v>
       </c>
       <c r="AC4" s="2">
         <v>1357355</v>
@@ -1518,8 +1638,52 @@
         <f>SUM(S4:V4)</f>
         <v>23275329</v>
       </c>
-    </row>
-    <row r="5" spans="2:114" x14ac:dyDescent="0.15">
+      <c r="AS4" s="2">
+        <f>AR4*1.1</f>
+        <v>25602861.900000002</v>
+      </c>
+      <c r="AT4" s="2">
+        <f t="shared" ref="AT4:BC4" si="3">AS4*1.1</f>
+        <v>28163148.090000004</v>
+      </c>
+      <c r="AU4" s="2">
+        <f t="shared" si="3"/>
+        <v>30979462.899000008</v>
+      </c>
+      <c r="AV4" s="2">
+        <f t="shared" si="3"/>
+        <v>34077409.188900009</v>
+      </c>
+      <c r="AW4" s="2">
+        <f t="shared" si="3"/>
+        <v>37485150.107790016</v>
+      </c>
+      <c r="AX4" s="2">
+        <f t="shared" si="3"/>
+        <v>41233665.118569024</v>
+      </c>
+      <c r="AY4" s="2">
+        <f t="shared" si="3"/>
+        <v>45357031.63042593</v>
+      </c>
+      <c r="AZ4" s="2">
+        <f t="shared" si="3"/>
+        <v>49892734.793468527</v>
+      </c>
+      <c r="BA4" s="2">
+        <f t="shared" si="3"/>
+        <v>54882008.272815384</v>
+      </c>
+      <c r="BB4" s="2">
+        <f t="shared" si="3"/>
+        <v>60370209.100096926</v>
+      </c>
+      <c r="BC4" s="2">
+        <f t="shared" si="3"/>
+        <v>66407230.010106623</v>
+      </c>
+    </row>
+    <row r="5" spans="2:114" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
@@ -1528,71 +1692,71 @@
         <v>3294771</v>
       </c>
       <c r="D5" s="6">
-        <f t="shared" ref="D5:T5" si="1">D3-D4</f>
+        <f t="shared" ref="D5:T5" si="4">D3-D4</f>
         <v>3323769</v>
       </c>
       <c r="E5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>3276878</v>
       </c>
       <c r="F5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>2469743</v>
       </c>
       <c r="G5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>3583062</v>
       </c>
       <c r="H5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>3279386</v>
       </c>
       <c r="I5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>3136924</v>
       </c>
       <c r="J5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>2447893</v>
       </c>
       <c r="K5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>3357878</v>
       </c>
       <c r="L5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>3513831</v>
       </c>
       <c r="M5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>3610880</v>
       </c>
       <c r="N5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>3525340</v>
       </c>
       <c r="O5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>4393367</v>
       </c>
       <c r="P5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>4385167</v>
       </c>
       <c r="Q5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>4704819</v>
       </c>
       <c r="R5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>4479149</v>
       </c>
       <c r="S5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>5279654</v>
       </c>
       <c r="T5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>5753855</v>
       </c>
       <c r="U5" s="6">
@@ -1600,75 +1764,135 @@
         <v>5346057</v>
       </c>
       <c r="V5" s="6">
-        <f t="shared" ref="V5" si="2">V3-V4</f>
+        <f t="shared" ref="V5:X5" si="5">V3-V4</f>
         <v>5528141</v>
       </c>
+      <c r="W5" s="6">
+        <f t="shared" si="5"/>
+        <v>5807619.4000000013</v>
+      </c>
+      <c r="X5" s="6">
+        <f t="shared" si="5"/>
+        <v>6329240.5000000009</v>
+      </c>
+      <c r="Y5" s="6">
+        <f>Y3-Y4</f>
+        <v>5880662.7000000002</v>
+      </c>
+      <c r="Z5" s="6">
+        <f t="shared" ref="Z5" si="6">Z3-Z4</f>
+        <v>6080955.1000000006</v>
+      </c>
       <c r="AC5" s="2">
-        <f t="shared" ref="AC5:AQ5" si="3">AC3-AC4</f>
+        <f t="shared" ref="AC5:AQ5" si="7">AC3-AC4</f>
         <v>805270</v>
       </c>
       <c r="AD5" s="2">
-        <f t="shared" ref="AD5:AG5" si="4">AD3-AD4</f>
+        <f t="shared" ref="AD5:AG5" si="8">AD3-AD4</f>
         <v>1164676</v>
       </c>
       <c r="AE5" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>983416</v>
       </c>
       <c r="AF5" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1257359</v>
       </c>
       <c r="AG5" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1751896</v>
       </c>
       <c r="AH5" s="2">
-        <f t="shared" ref="AH5:AL5" si="5">AH3-AH4</f>
+        <f t="shared" ref="AH5:AL5" si="9">AH3-AH4</f>
         <v>2188035</v>
       </c>
       <c r="AI5" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>2573207</v>
       </c>
       <c r="AJ5" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3659713</v>
       </c>
       <c r="AK5" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>5826803</v>
       </c>
       <c r="AL5" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>7716234</v>
       </c>
       <c r="AM5" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>9719737</v>
       </c>
       <c r="AN5" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>12365161</v>
       </c>
       <c r="AO5" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>12447265</v>
       </c>
       <c r="AP5" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>14007929</v>
       </c>
       <c r="AQ5" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>17962502</v>
       </c>
       <c r="AR5" s="2">
         <f>AR3-AR4</f>
         <v>21907707</v>
       </c>
-    </row>
-    <row r="6" spans="2:114" x14ac:dyDescent="0.15">
+      <c r="AS5" s="2">
+        <f t="shared" ref="AS5" si="10">AS3-AS4</f>
+        <v>24098477.699999999</v>
+      </c>
+      <c r="AT5" s="2">
+        <f t="shared" ref="AT5:BC5" si="11">AT3-AT4</f>
+        <v>26508325.469999999</v>
+      </c>
+      <c r="AU5" s="2">
+        <f t="shared" si="11"/>
+        <v>29159158.017000001</v>
+      </c>
+      <c r="AV5" s="2">
+        <f t="shared" si="11"/>
+        <v>32075073.818700008</v>
+      </c>
+      <c r="AW5" s="2">
+        <f t="shared" si="11"/>
+        <v>35282581.20057001</v>
+      </c>
+      <c r="AX5" s="2">
+        <f t="shared" si="11"/>
+        <v>38810839.320627011</v>
+      </c>
+      <c r="AY5" s="2">
+        <f t="shared" si="11"/>
+        <v>42691923.252689719</v>
+      </c>
+      <c r="AZ5" s="2">
+        <f t="shared" si="11"/>
+        <v>46961115.577958696</v>
+      </c>
+      <c r="BA5" s="2">
+        <f t="shared" si="11"/>
+        <v>51657227.135754563</v>
+      </c>
+      <c r="BB5" s="2">
+        <f t="shared" si="11"/>
+        <v>56822949.849330023</v>
+      </c>
+      <c r="BC5" s="2">
+        <f t="shared" si="11"/>
+        <v>62505244.834263027</v>
+      </c>
+    </row>
+    <row r="6" spans="2:114" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
@@ -1731,6 +1955,22 @@
       </c>
       <c r="V6" s="6">
         <v>1113376</v>
+      </c>
+      <c r="W6" s="6">
+        <f t="shared" ref="W6:W8" si="12">S6*1.1</f>
+        <v>757207.00000000012</v>
+      </c>
+      <c r="X6" s="6">
+        <f t="shared" ref="X6:X8" si="13">T6*1.1</f>
+        <v>784591.50000000012</v>
+      </c>
+      <c r="Y6" s="6">
+        <f t="shared" ref="Y6:Y8" si="14">U6*1.1</f>
+        <v>864924.50000000012</v>
+      </c>
+      <c r="Z6" s="6">
+        <f t="shared" ref="Z6:Z8" si="15">V6*1.1</f>
+        <v>1224713.6000000001</v>
       </c>
       <c r="AC6" s="2">
         <v>293839</v>
@@ -1781,11 +2021,55 @@
         <v>2917554</v>
       </c>
       <c r="AR6" s="2">
-        <f t="shared" ref="AR6:AR8" si="6">SUM(S6:V6)</f>
+        <f t="shared" ref="AR6:AR8" si="16">SUM(S6:V6)</f>
         <v>3301306</v>
       </c>
-    </row>
-    <row r="7" spans="2:114" x14ac:dyDescent="0.15">
+      <c r="AS6" s="2">
+        <f>AR6*1.1</f>
+        <v>3631436.6</v>
+      </c>
+      <c r="AT6" s="2">
+        <f t="shared" ref="AT6:BC6" si="17">AS6*1.1</f>
+        <v>3994580.2600000002</v>
+      </c>
+      <c r="AU6" s="2">
+        <f t="shared" si="17"/>
+        <v>4394038.2860000003</v>
+      </c>
+      <c r="AV6" s="2">
+        <f t="shared" si="17"/>
+        <v>4833442.1146000009</v>
+      </c>
+      <c r="AW6" s="2">
+        <f t="shared" si="17"/>
+        <v>5316786.3260600017</v>
+      </c>
+      <c r="AX6" s="2">
+        <f t="shared" si="17"/>
+        <v>5848464.9586660024</v>
+      </c>
+      <c r="AY6" s="2">
+        <f t="shared" si="17"/>
+        <v>6433311.4545326028</v>
+      </c>
+      <c r="AZ6" s="2">
+        <f t="shared" si="17"/>
+        <v>7076642.599985864</v>
+      </c>
+      <c r="BA6" s="2">
+        <f t="shared" si="17"/>
+        <v>7784306.859984451</v>
+      </c>
+      <c r="BB6" s="2">
+        <f t="shared" si="17"/>
+        <v>8562737.5459828973</v>
+      </c>
+      <c r="BC6" s="2">
+        <f t="shared" si="17"/>
+        <v>9419011.300581187</v>
+      </c>
+    </row>
+    <row r="7" spans="2:114" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
@@ -1848,6 +2132,22 @@
       </c>
       <c r="V7" s="6">
         <v>890300</v>
+      </c>
+      <c r="W7" s="6">
+        <f t="shared" si="12"/>
+        <v>905105.3</v>
+      </c>
+      <c r="X7" s="6">
+        <f t="shared" si="13"/>
+        <v>907151.3</v>
+      </c>
+      <c r="Y7" s="6">
+        <f t="shared" si="14"/>
+        <v>938942.4</v>
+      </c>
+      <c r="Z7" s="6">
+        <f t="shared" si="15"/>
+        <v>979330.00000000012</v>
       </c>
       <c r="AC7" s="2">
         <v>163329</v>
@@ -1898,11 +2198,55 @@
         <v>2925295</v>
       </c>
       <c r="AR7" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>3391390</v>
       </c>
-    </row>
-    <row r="8" spans="2:114" x14ac:dyDescent="0.15">
+      <c r="AS7" s="2">
+        <f>AR7*1.1</f>
+        <v>3730529.0000000005</v>
+      </c>
+      <c r="AT7" s="2">
+        <f t="shared" ref="AT7:BC7" si="18">AS7*1.1</f>
+        <v>4103581.9000000008</v>
+      </c>
+      <c r="AU7" s="2">
+        <f t="shared" si="18"/>
+        <v>4513940.0900000017</v>
+      </c>
+      <c r="AV7" s="2">
+        <f t="shared" si="18"/>
+        <v>4965334.0990000023</v>
+      </c>
+      <c r="AW7" s="2">
+        <f t="shared" si="18"/>
+        <v>5461867.5089000026</v>
+      </c>
+      <c r="AX7" s="2">
+        <f t="shared" si="18"/>
+        <v>6008054.2597900033</v>
+      </c>
+      <c r="AY7" s="2">
+        <f t="shared" si="18"/>
+        <v>6608859.6857690038</v>
+      </c>
+      <c r="AZ7" s="2">
+        <f t="shared" si="18"/>
+        <v>7269745.6543459045</v>
+      </c>
+      <c r="BA7" s="2">
+        <f t="shared" si="18"/>
+        <v>7996720.2197804954</v>
+      </c>
+      <c r="BB7" s="2">
+        <f t="shared" si="18"/>
+        <v>8796392.2417585459</v>
+      </c>
+      <c r="BC7" s="2">
+        <f t="shared" si="18"/>
+        <v>9676031.4659344014</v>
+      </c>
+    </row>
+    <row r="8" spans="2:114" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
@@ -1965,6 +2309,22 @@
       </c>
       <c r="V8" s="6">
         <v>567802</v>
+      </c>
+      <c r="W8" s="6">
+        <f t="shared" si="12"/>
+        <v>463608.2</v>
+      </c>
+      <c r="X8" s="6">
+        <f t="shared" si="13"/>
+        <v>485334.30000000005</v>
+      </c>
+      <c r="Y8" s="6">
+        <f t="shared" si="14"/>
+        <v>503724.10000000003</v>
+      </c>
+      <c r="Z8" s="6">
+        <f t="shared" si="15"/>
+        <v>624582.20000000007</v>
       </c>
       <c r="AC8" s="2">
         <f>70555-(6094)</f>
@@ -2016,84 +2376,128 @@
         <v>1702039</v>
       </c>
       <c r="AR8" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>1888408</v>
       </c>
-    </row>
-    <row r="9" spans="2:114" x14ac:dyDescent="0.15">
+      <c r="AS8" s="2">
+        <f>AR8*1.1</f>
+        <v>2077248.8000000003</v>
+      </c>
+      <c r="AT8" s="2">
+        <f t="shared" ref="AT8:BC8" si="19">AS8*1.1</f>
+        <v>2284973.6800000006</v>
+      </c>
+      <c r="AU8" s="2">
+        <f t="shared" si="19"/>
+        <v>2513471.0480000009</v>
+      </c>
+      <c r="AV8" s="2">
+        <f t="shared" si="19"/>
+        <v>2764818.1528000012</v>
+      </c>
+      <c r="AW8" s="2">
+        <f t="shared" si="19"/>
+        <v>3041299.9680800014</v>
+      </c>
+      <c r="AX8" s="2">
+        <f t="shared" si="19"/>
+        <v>3345429.9648880018</v>
+      </c>
+      <c r="AY8" s="2">
+        <f t="shared" si="19"/>
+        <v>3679972.9613768021</v>
+      </c>
+      <c r="AZ8" s="2">
+        <f t="shared" si="19"/>
+        <v>4047970.2575144828</v>
+      </c>
+      <c r="BA8" s="2">
+        <f t="shared" si="19"/>
+        <v>4452767.2832659315</v>
+      </c>
+      <c r="BB8" s="2">
+        <f t="shared" si="19"/>
+        <v>4898044.0115925251</v>
+      </c>
+      <c r="BC8" s="2">
+        <f t="shared" si="19"/>
+        <v>5387848.412751778</v>
+      </c>
+    </row>
+    <row r="9" spans="2:114" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="6">
-        <f t="shared" ref="C9:T9" si="7">SUM(C6:C8)</f>
+        <f t="shared" ref="C9:T9" si="20">SUM(C6:C8)</f>
         <v>1334915</v>
       </c>
       <c r="D9" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>1476139</v>
       </c>
       <c r="E9" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>1521625</v>
       </c>
       <c r="F9" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>1837973</v>
       </c>
       <c r="G9" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>1611436</v>
       </c>
       <c r="H9" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>1701103</v>
       </c>
       <c r="I9" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>1603906</v>
       </c>
       <c r="J9" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>1897989</v>
       </c>
       <c r="K9" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>1643561</v>
       </c>
       <c r="L9" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>1686648</v>
       </c>
       <c r="M9" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>1694486</v>
       </c>
       <c r="N9" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>2029231</v>
       </c>
       <c r="O9" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>1760833</v>
       </c>
       <c r="P9" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>1782330</v>
       </c>
       <c r="Q9" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>1795342</v>
       </c>
       <c r="R9" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>2206383</v>
       </c>
       <c r="S9" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>1932655</v>
       </c>
       <c r="T9" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>1979161</v>
       </c>
       <c r="U9" s="6">
@@ -2101,148 +2505,208 @@
         <v>2097810</v>
       </c>
       <c r="V9" s="6">
-        <f t="shared" ref="V9" si="8">SUM(V6:V8)</f>
+        <f t="shared" ref="V9:X9" si="21">SUM(V6:V8)</f>
         <v>2571478</v>
       </c>
+      <c r="W9" s="6">
+        <f t="shared" si="21"/>
+        <v>2125920.5000000005</v>
+      </c>
+      <c r="X9" s="6">
+        <f t="shared" si="21"/>
+        <v>2177077.1000000006</v>
+      </c>
+      <c r="Y9" s="6">
+        <f>SUM(Y6:Y8)</f>
+        <v>2307591</v>
+      </c>
+      <c r="Z9" s="6">
+        <f t="shared" ref="Z9" si="22">SUM(Z6:Z8)</f>
+        <v>2828625.8000000003</v>
+      </c>
       <c r="AC9" s="2">
-        <f t="shared" ref="AC9:AQ9" si="9">SUM(AC6:AC8)</f>
+        <f t="shared" ref="AC9:AQ9" si="23">SUM(AC6:AC8)</f>
         <v>521629</v>
       </c>
       <c r="AD9" s="2">
-        <f t="shared" ref="AD9:AG9" si="10">SUM(AD6:AD8)</f>
+        <f t="shared" ref="AD9:AG9" si="24">SUM(AD6:AD8)</f>
         <v>788608</v>
       </c>
       <c r="AE9" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="24"/>
         <v>933424</v>
       </c>
       <c r="AF9" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="24"/>
         <v>1029012</v>
       </c>
       <c r="AG9" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="24"/>
         <v>1349248</v>
       </c>
       <c r="AH9" s="2">
-        <f t="shared" ref="AH9:AL9" si="11">SUM(AH6:AH8)</f>
+        <f t="shared" ref="AH9:AL9" si="25">SUM(AH6:AH8)</f>
         <v>1882209</v>
       </c>
       <c r="AI9" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v>2193414</v>
       </c>
       <c r="AJ9" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v>2821034</v>
       </c>
       <c r="AK9" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v>4221577</v>
       </c>
       <c r="AL9" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v>5110980</v>
       </c>
       <c r="AM9" s="2">
-        <f t="shared" ref="AM9:AN9" si="12">SUM(AM6:AM8)</f>
+        <f t="shared" ref="AM9:AN9" si="26">SUM(AM6:AM8)</f>
         <v>5134448</v>
       </c>
       <c r="AN9" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="26"/>
         <v>6170652</v>
       </c>
       <c r="AO9" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="23"/>
         <v>6814434</v>
       </c>
       <c r="AP9" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="23"/>
         <v>7053926</v>
       </c>
       <c r="AQ9" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="23"/>
         <v>7544888</v>
       </c>
       <c r="AR9" s="2">
         <f>SUM(AR6:AR8)</f>
         <v>8581104</v>
       </c>
-    </row>
-    <row r="10" spans="2:114" x14ac:dyDescent="0.15">
+      <c r="AS9" s="2">
+        <f t="shared" ref="AS9" si="27">SUM(AS6:AS8)</f>
+        <v>9439214.4000000004</v>
+      </c>
+      <c r="AT9" s="2">
+        <f t="shared" ref="AT9:BC9" si="28">SUM(AT6:AT8)</f>
+        <v>10383135.840000002</v>
+      </c>
+      <c r="AU9" s="2">
+        <f t="shared" si="28"/>
+        <v>11421449.424000002</v>
+      </c>
+      <c r="AV9" s="2">
+        <f t="shared" si="28"/>
+        <v>12563594.366400003</v>
+      </c>
+      <c r="AW9" s="2">
+        <f t="shared" si="28"/>
+        <v>13819953.803040005</v>
+      </c>
+      <c r="AX9" s="2">
+        <f t="shared" si="28"/>
+        <v>15201949.183344007</v>
+      </c>
+      <c r="AY9" s="2">
+        <f t="shared" si="28"/>
+        <v>16722144.101678409</v>
+      </c>
+      <c r="AZ9" s="2">
+        <f t="shared" si="28"/>
+        <v>18394358.511846252</v>
+      </c>
+      <c r="BA9" s="2">
+        <f t="shared" si="28"/>
+        <v>20233794.363030881</v>
+      </c>
+      <c r="BB9" s="2">
+        <f t="shared" si="28"/>
+        <v>22257173.799333971</v>
+      </c>
+      <c r="BC9" s="2">
+        <f t="shared" si="28"/>
+        <v>24482891.179267369</v>
+      </c>
+    </row>
+    <row r="10" spans="2:114" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="6">
-        <f t="shared" ref="C10:T10" si="13">C5-C9</f>
+        <f t="shared" ref="C10:T10" si="29">C5-C9</f>
         <v>1959856</v>
       </c>
       <c r="D10" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="29"/>
         <v>1847630</v>
       </c>
       <c r="E10" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="29"/>
         <v>1755253</v>
       </c>
       <c r="F10" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="29"/>
         <v>631770</v>
       </c>
       <c r="G10" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="29"/>
         <v>1971626</v>
       </c>
       <c r="H10" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="29"/>
         <v>1578283</v>
       </c>
       <c r="I10" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="29"/>
         <v>1533018</v>
       </c>
       <c r="J10" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="29"/>
         <v>549904</v>
       </c>
       <c r="K10" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="29"/>
         <v>1714317</v>
       </c>
       <c r="L10" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="29"/>
         <v>1827183</v>
       </c>
       <c r="M10" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="29"/>
         <v>1916394</v>
       </c>
       <c r="N10" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="29"/>
         <v>1496109</v>
       </c>
       <c r="O10" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="29"/>
         <v>2632534</v>
       </c>
       <c r="P10" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="29"/>
         <v>2602837</v>
       </c>
       <c r="Q10" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="29"/>
         <v>2909477</v>
       </c>
       <c r="R10" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="29"/>
         <v>2272766</v>
       </c>
       <c r="S10" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="29"/>
         <v>3346999</v>
       </c>
       <c r="T10" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="29"/>
         <v>3774694</v>
       </c>
       <c r="U10" s="6">
@@ -2250,75 +2714,135 @@
         <v>3248247</v>
       </c>
       <c r="V10" s="6">
-        <f t="shared" ref="V10" si="14">V5-V9</f>
+        <f t="shared" ref="V10:X10" si="30">V5-V9</f>
         <v>2956663</v>
       </c>
+      <c r="W10" s="6">
+        <f t="shared" si="30"/>
+        <v>3681698.9000000008</v>
+      </c>
+      <c r="X10" s="6">
+        <f t="shared" si="30"/>
+        <v>4152163.4000000004</v>
+      </c>
+      <c r="Y10" s="6">
+        <f>Y5-Y9</f>
+        <v>3573071.7</v>
+      </c>
+      <c r="Z10" s="6">
+        <f t="shared" ref="Z10" si="31">Z5-Z9</f>
+        <v>3252329.3000000003</v>
+      </c>
       <c r="AC10" s="2">
-        <f t="shared" ref="AC10:AQ10" si="15">AC5-AC9</f>
+        <f t="shared" ref="AC10:AQ10" si="32">AC5-AC9</f>
         <v>283641</v>
       </c>
       <c r="AD10" s="2">
-        <f t="shared" ref="AD10:AG10" si="16">AD5-AD9</f>
+        <f t="shared" ref="AD10:AG10" si="33">AD5-AD9</f>
         <v>376068</v>
       </c>
       <c r="AE10" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="33"/>
         <v>49992</v>
       </c>
       <c r="AF10" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="33"/>
         <v>228347</v>
       </c>
       <c r="AG10" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="33"/>
         <v>402648</v>
       </c>
       <c r="AH10" s="2">
-        <f t="shared" ref="AH10:AL10" si="17">AH5-AH9</f>
+        <f t="shared" ref="AH10:AL10" si="34">AH5-AH9</f>
         <v>305826</v>
       </c>
       <c r="AI10" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="34"/>
         <v>379793</v>
       </c>
       <c r="AJ10" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="34"/>
         <v>838679</v>
       </c>
       <c r="AK10" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="34"/>
         <v>1605226</v>
       </c>
       <c r="AL10" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="34"/>
         <v>2605254</v>
       </c>
       <c r="AM10" s="2">
-        <f t="shared" ref="AM10:AN10" si="18">AM5-AM9</f>
+        <f t="shared" ref="AM10:AN10" si="35">AM5-AM9</f>
         <v>4585289</v>
       </c>
       <c r="AN10" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="35"/>
         <v>6194509</v>
       </c>
       <c r="AO10" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="32"/>
         <v>5632831</v>
       </c>
       <c r="AP10" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="32"/>
         <v>6954003</v>
       </c>
       <c r="AQ10" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="32"/>
         <v>10417614</v>
       </c>
       <c r="AR10" s="2">
         <f>AR5-AR9</f>
         <v>13326603</v>
       </c>
-    </row>
-    <row r="11" spans="2:114" x14ac:dyDescent="0.15">
+      <c r="AS10" s="2">
+        <f t="shared" ref="AS10" si="36">AS5-AS9</f>
+        <v>14659263.299999999</v>
+      </c>
+      <c r="AT10" s="2">
+        <f t="shared" ref="AT10:BC10" si="37">AT5-AT9</f>
+        <v>16125189.629999997</v>
+      </c>
+      <c r="AU10" s="2">
+        <f t="shared" si="37"/>
+        <v>17737708.592999998</v>
+      </c>
+      <c r="AV10" s="2">
+        <f t="shared" si="37"/>
+        <v>19511479.452300005</v>
+      </c>
+      <c r="AW10" s="2">
+        <f t="shared" si="37"/>
+        <v>21462627.397530004</v>
+      </c>
+      <c r="AX10" s="2">
+        <f t="shared" si="37"/>
+        <v>23608890.137283005</v>
+      </c>
+      <c r="AY10" s="2">
+        <f t="shared" si="37"/>
+        <v>25969779.151011311</v>
+      </c>
+      <c r="AZ10" s="2">
+        <f t="shared" si="37"/>
+        <v>28566757.066112444</v>
+      </c>
+      <c r="BA10" s="2">
+        <f t="shared" si="37"/>
+        <v>31423432.772723682</v>
+      </c>
+      <c r="BB10" s="2">
+        <f t="shared" si="37"/>
+        <v>34565776.049996048</v>
+      </c>
+      <c r="BC10" s="2">
+        <f t="shared" si="37"/>
+        <v>38022353.654995658</v>
+      </c>
+    </row>
+    <row r="11" spans="2:114" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
@@ -2380,6 +2904,18 @@
         <v>-175294</v>
       </c>
       <c r="V11" s="6">
+        <v>-234395</v>
+      </c>
+      <c r="W11" s="6">
+        <v>-184172</v>
+      </c>
+      <c r="X11" s="6">
+        <v>-182649</v>
+      </c>
+      <c r="Y11" s="6">
+        <v>-175294</v>
+      </c>
+      <c r="Z11" s="6">
         <v>-234395</v>
       </c>
       <c r="AC11" s="2">
@@ -2434,8 +2970,52 @@
         <f>SUM(S11:V11)</f>
         <v>-776510</v>
       </c>
-    </row>
-    <row r="12" spans="2:114" x14ac:dyDescent="0.15">
+      <c r="AS11" s="2">
+        <f>+AR23*$AT$28</f>
+        <v>-108009.54000000001</v>
+      </c>
+      <c r="AT11" s="2">
+        <f>+AS23*$AT$28</f>
+        <v>221464.1942</v>
+      </c>
+      <c r="AU11" s="2">
+        <f t="shared" ref="AT11:BC11" si="38">+AT23*$AT$28</f>
+        <v>587027.01163399999</v>
+      </c>
+      <c r="AV11" s="2">
+        <f t="shared" si="38"/>
+        <v>992341.60072417988</v>
+      </c>
+      <c r="AW11" s="2">
+        <f t="shared" si="38"/>
+        <v>1441437.5416320388</v>
+      </c>
+      <c r="AX11" s="2">
+        <f t="shared" si="38"/>
+        <v>1938747.9852550232</v>
+      </c>
+      <c r="AY11" s="2">
+        <f t="shared" si="38"/>
+        <v>2489149.9987875144</v>
+      </c>
+      <c r="AZ11" s="2">
+        <f t="shared" si="38"/>
+        <v>3098008.9444193086</v>
+      </c>
+      <c r="BA11" s="2">
+        <f t="shared" si="38"/>
+        <v>3771227.294397552</v>
+      </c>
+      <c r="BB11" s="2">
+        <f t="shared" si="38"/>
+        <v>4515298.3259959659</v>
+      </c>
+      <c r="BC11" s="2">
+        <f t="shared" si="38"/>
+        <v>5337365.1842845939</v>
+      </c>
+    </row>
+    <row r="12" spans="2:114" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
@@ -2497,6 +3077,18 @@
         <v>36457</v>
       </c>
       <c r="V12" s="6">
+        <v>45473</v>
+      </c>
+      <c r="W12" s="6">
+        <v>50899</v>
+      </c>
+      <c r="X12" s="6">
+        <v>39630</v>
+      </c>
+      <c r="Y12" s="6">
+        <v>36457</v>
+      </c>
+      <c r="Z12" s="6">
         <v>45473</v>
       </c>
       <c r="AC12" s="2">
@@ -2552,81 +3144,125 @@
         <f>SUM(S12:V12)</f>
         <v>172459</v>
       </c>
-    </row>
-    <row r="13" spans="2:114" x14ac:dyDescent="0.15">
+      <c r="AS12" s="2">
+        <f>AR12*1.05</f>
+        <v>181081.95</v>
+      </c>
+      <c r="AT12" s="2">
+        <f t="shared" ref="AT12:BC12" si="39">AS12*1.05</f>
+        <v>190136.04750000002</v>
+      </c>
+      <c r="AU12" s="2">
+        <f t="shared" si="39"/>
+        <v>199642.84987500001</v>
+      </c>
+      <c r="AV12" s="2">
+        <f t="shared" si="39"/>
+        <v>209624.99236875001</v>
+      </c>
+      <c r="AW12" s="2">
+        <f t="shared" si="39"/>
+        <v>220106.24198718753</v>
+      </c>
+      <c r="AX12" s="2">
+        <f t="shared" si="39"/>
+        <v>231111.55408654691</v>
+      </c>
+      <c r="AY12" s="2">
+        <f t="shared" si="39"/>
+        <v>242667.13179087426</v>
+      </c>
+      <c r="AZ12" s="2">
+        <f t="shared" si="39"/>
+        <v>254800.48838041798</v>
+      </c>
+      <c r="BA12" s="2">
+        <f t="shared" si="39"/>
+        <v>267540.5127994389</v>
+      </c>
+      <c r="BB12" s="2">
+        <f t="shared" si="39"/>
+        <v>280917.53843941086</v>
+      </c>
+      <c r="BC12" s="2">
+        <f t="shared" si="39"/>
+        <v>294963.41536138143</v>
+      </c>
+    </row>
+    <row r="13" spans="2:114" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="6">
-        <f t="shared" ref="C13:T13" si="19">C10+C11+C12</f>
+        <f t="shared" ref="C13:T13" si="40">C10+C11+C12</f>
         <v>2034502</v>
       </c>
       <c r="D13" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="40"/>
         <v>1593789</v>
       </c>
       <c r="E13" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="40"/>
         <v>1660959</v>
       </c>
       <c r="F13" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="40"/>
         <v>550853</v>
       </c>
       <c r="G13" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="40"/>
         <v>1979692</v>
       </c>
       <c r="H13" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="40"/>
         <v>1623054</v>
       </c>
       <c r="I13" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="40"/>
         <v>1621847</v>
       </c>
       <c r="J13" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="40"/>
         <v>39336</v>
       </c>
       <c r="K13" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="40"/>
         <v>1468874</v>
       </c>
       <c r="L13" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="40"/>
         <v>1679332</v>
       </c>
       <c r="M13" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="40"/>
         <v>1909049</v>
       </c>
       <c r="N13" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="40"/>
         <v>1148150</v>
       </c>
       <c r="O13" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="40"/>
         <v>2614579</v>
       </c>
       <c r="P13" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="40"/>
         <v>2513856</v>
       </c>
       <c r="Q13" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="40"/>
         <v>2702954</v>
       </c>
       <c r="R13" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="40"/>
         <v>2134268</v>
       </c>
       <c r="S13" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="40"/>
         <v>3213726</v>
       </c>
       <c r="T13" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="40"/>
         <v>3631675</v>
       </c>
       <c r="U13" s="6">
@@ -2634,75 +3270,135 @@
         <v>3109410</v>
       </c>
       <c r="V13" s="6">
-        <f t="shared" ref="V13" si="20">V10+V11+V12</f>
+        <f t="shared" ref="V13:X13" si="41">V10+V11+V12</f>
         <v>2767741</v>
       </c>
+      <c r="W13" s="6">
+        <f t="shared" si="41"/>
+        <v>3548425.9000000008</v>
+      </c>
+      <c r="X13" s="6">
+        <f t="shared" si="41"/>
+        <v>4009144.4000000004</v>
+      </c>
+      <c r="Y13" s="6">
+        <f>Y10+Y11+Y12</f>
+        <v>3434234.7</v>
+      </c>
+      <c r="Z13" s="6">
+        <f t="shared" ref="Z13" si="42">Z10+Z11+Z12</f>
+        <v>3063407.3000000003</v>
+      </c>
       <c r="AC13" s="6">
-        <f t="shared" ref="AC13:AG13" si="21">AC10+AC11+AC12</f>
+        <f t="shared" ref="AC13:AG13" si="43">AC10+AC11+AC12</f>
         <v>267696</v>
       </c>
       <c r="AD13" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="43"/>
         <v>359522</v>
       </c>
       <c r="AE13" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="43"/>
         <v>30480</v>
       </c>
       <c r="AF13" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="43"/>
         <v>171074</v>
       </c>
       <c r="AG13" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="43"/>
         <v>349369</v>
       </c>
       <c r="AH13" s="6">
-        <f t="shared" ref="AH13:AL13" si="22">AH10+AH11+AH12</f>
+        <f t="shared" ref="AH13:AL13" si="44">AH10+AH11+AH12</f>
         <v>141885</v>
       </c>
       <c r="AI13" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="44"/>
         <v>260507</v>
       </c>
       <c r="AJ13" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="44"/>
         <v>485321</v>
       </c>
       <c r="AK13" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="44"/>
         <v>1226458</v>
       </c>
       <c r="AL13" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="44"/>
         <v>2063231</v>
       </c>
       <c r="AM13" s="6">
-        <f t="shared" ref="AM13:AN13" si="23">AM10+AM11+AM12</f>
+        <f t="shared" ref="AM13:AN13" si="45">AM10+AM11+AM12</f>
         <v>3199349</v>
       </c>
       <c r="AN13" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="45"/>
         <v>5840103</v>
       </c>
       <c r="AO13" s="6">
-        <f t="shared" ref="AO13" si="24">AO10+AO11+AO12</f>
+        <f t="shared" ref="AO13" si="46">AO10+AO11+AO12</f>
         <v>5263929</v>
       </c>
       <c r="AP13" s="6">
-        <f t="shared" ref="AP13" si="25">AP10+AP11+AP12</f>
+        <f t="shared" ref="AP13" si="47">AP10+AP11+AP12</f>
         <v>6205405</v>
       </c>
       <c r="AQ13" s="6">
-        <f t="shared" ref="AQ13" si="26">AQ10+AQ11+AQ12</f>
+        <f t="shared" ref="AQ13" si="48">AQ10+AQ11+AQ12</f>
         <v>9965657</v>
       </c>
       <c r="AR13" s="6">
-        <f t="shared" ref="AR13" si="27">AR10+AR11+AR12</f>
+        <f t="shared" ref="AR13:AS13" si="49">AR10+AR11+AR12</f>
         <v>12722552</v>
       </c>
-    </row>
-    <row r="14" spans="2:114" x14ac:dyDescent="0.15">
+      <c r="AS13" s="6">
+        <f t="shared" si="49"/>
+        <v>14732335.709999999</v>
+      </c>
+      <c r="AT13" s="6">
+        <f t="shared" ref="AT13:BC13" si="50">AT10+AT11+AT12</f>
+        <v>16536789.871699996</v>
+      </c>
+      <c r="AU13" s="6">
+        <f t="shared" si="50"/>
+        <v>18524378.454508997</v>
+      </c>
+      <c r="AV13" s="6">
+        <f t="shared" si="50"/>
+        <v>20713446.045392934</v>
+      </c>
+      <c r="AW13" s="6">
+        <f t="shared" si="50"/>
+        <v>23124171.181149229</v>
+      </c>
+      <c r="AX13" s="6">
+        <f t="shared" si="50"/>
+        <v>25778749.676624574</v>
+      </c>
+      <c r="AY13" s="6">
+        <f t="shared" si="50"/>
+        <v>28701596.281589698</v>
+      </c>
+      <c r="AZ13" s="6">
+        <f t="shared" si="50"/>
+        <v>31919566.498912171</v>
+      </c>
+      <c r="BA13" s="6">
+        <f t="shared" si="50"/>
+        <v>35462200.579920679</v>
+      </c>
+      <c r="BB13" s="6">
+        <f t="shared" si="50"/>
+        <v>39361991.914431423</v>
+      </c>
+      <c r="BC13" s="6">
+        <f t="shared" si="50"/>
+        <v>43654682.25464163</v>
+      </c>
+    </row>
+    <row r="14" spans="2:114" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>17</v>
       </c>
@@ -2764,6 +3460,18 @@
         <v>-562494</v>
       </c>
       <c r="V14" s="6">
+        <v>-349220</v>
+      </c>
+      <c r="W14" s="6">
+        <v>-323375</v>
+      </c>
+      <c r="X14" s="6">
+        <v>-506262</v>
+      </c>
+      <c r="Y14" s="6">
+        <v>-562494</v>
+      </c>
+      <c r="Z14" s="6">
         <v>-349220</v>
       </c>
       <c r="AC14" s="2">
@@ -2819,81 +3527,125 @@
         <f>SUM(S14:V14)</f>
         <v>-1741351</v>
       </c>
-    </row>
-    <row r="15" spans="2:114" x14ac:dyDescent="0.15">
+      <c r="AS14" s="2">
+        <f>AR14</f>
+        <v>-1741351</v>
+      </c>
+      <c r="AT14" s="2">
+        <f t="shared" ref="AT14:BC14" si="51">AS14</f>
+        <v>-1741351</v>
+      </c>
+      <c r="AU14" s="2">
+        <f t="shared" si="51"/>
+        <v>-1741351</v>
+      </c>
+      <c r="AV14" s="2">
+        <f t="shared" si="51"/>
+        <v>-1741351</v>
+      </c>
+      <c r="AW14" s="2">
+        <f t="shared" si="51"/>
+        <v>-1741351</v>
+      </c>
+      <c r="AX14" s="2">
+        <f t="shared" si="51"/>
+        <v>-1741351</v>
+      </c>
+      <c r="AY14" s="2">
+        <f t="shared" si="51"/>
+        <v>-1741351</v>
+      </c>
+      <c r="AZ14" s="2">
+        <f t="shared" si="51"/>
+        <v>-1741351</v>
+      </c>
+      <c r="BA14" s="2">
+        <f t="shared" si="51"/>
+        <v>-1741351</v>
+      </c>
+      <c r="BB14" s="2">
+        <f t="shared" si="51"/>
+        <v>-1741351</v>
+      </c>
+      <c r="BC14" s="2">
+        <f t="shared" si="51"/>
+        <v>-1741351</v>
+      </c>
+    </row>
+    <row r="15" spans="2:114" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="6">
-        <f t="shared" ref="C15:T15" si="28">C13+C14</f>
+        <f t="shared" ref="C15:T15" si="52">C13+C14</f>
         <v>1706715</v>
       </c>
       <c r="D15" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="52"/>
         <v>1353013</v>
       </c>
       <c r="E15" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="52"/>
         <v>1449071</v>
       </c>
       <c r="F15" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="52"/>
         <v>607429</v>
       </c>
       <c r="G15" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="52"/>
         <v>1597447</v>
       </c>
       <c r="H15" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="52"/>
         <v>1440951</v>
       </c>
       <c r="I15" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="52"/>
         <v>1398242</v>
       </c>
       <c r="J15" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="52"/>
         <v>55284</v>
       </c>
       <c r="K15" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="52"/>
         <v>1305120</v>
       </c>
       <c r="L15" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="52"/>
         <v>1487610</v>
       </c>
       <c r="M15" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="52"/>
         <v>1677422</v>
       </c>
       <c r="N15" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="52"/>
         <v>937838</v>
       </c>
       <c r="O15" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="52"/>
         <v>2332209</v>
       </c>
       <c r="P15" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="52"/>
         <v>2147306</v>
       </c>
       <c r="Q15" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="52"/>
         <v>2363509</v>
       </c>
       <c r="R15" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="52"/>
         <v>1868607</v>
       </c>
       <c r="S15" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="52"/>
         <v>2890351</v>
       </c>
       <c r="T15" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="52"/>
         <v>3125413</v>
       </c>
       <c r="U15" s="6">
@@ -2901,75 +3653,363 @@
         <v>2546916</v>
       </c>
       <c r="V15" s="6">
-        <f t="shared" ref="V15" si="29">V13+V14</f>
+        <f t="shared" ref="V15:X15" si="53">V13+V14</f>
         <v>2418521</v>
+      </c>
+      <c r="W15" s="6">
+        <f t="shared" si="53"/>
+        <v>3225050.9000000008</v>
+      </c>
+      <c r="X15" s="6">
+        <f t="shared" si="53"/>
+        <v>3502882.4000000004</v>
+      </c>
+      <c r="Y15" s="6">
+        <f>Y13+Y14</f>
+        <v>2871740.7</v>
+      </c>
+      <c r="Z15" s="6">
+        <f t="shared" ref="Z15" si="54">Z13+Z14</f>
+        <v>2714187.3000000003</v>
       </c>
       <c r="AC15" s="2">
         <f>AC13-AC14</f>
         <v>160853</v>
       </c>
       <c r="AD15" s="2">
-        <f t="shared" ref="AD15:AG15" si="30">AD13-AD14</f>
+        <f t="shared" ref="AD15:AG15" si="55">AD13-AD14</f>
         <v>226126</v>
       </c>
       <c r="AE15" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="55"/>
         <v>17152</v>
       </c>
       <c r="AF15" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="55"/>
         <v>112403</v>
       </c>
       <c r="AG15" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="55"/>
         <v>266799</v>
       </c>
       <c r="AH15" s="2">
-        <f t="shared" ref="AH15" si="31">AH13-AH14</f>
+        <f t="shared" ref="AH15" si="56">AH13-AH14</f>
         <v>122641</v>
       </c>
       <c r="AI15" s="2">
-        <f t="shared" ref="AI15" si="32">AI13-AI14</f>
+        <f t="shared" ref="AI15" si="57">AI13-AI14</f>
         <v>186678</v>
       </c>
       <c r="AJ15" s="2">
-        <f t="shared" ref="AJ15" si="33">AJ13-AJ14</f>
+        <f t="shared" ref="AJ15" si="58">AJ13-AJ14</f>
         <v>558929</v>
       </c>
       <c r="AK15" s="2">
-        <f t="shared" ref="AK15:AN15" si="34">AK13-AK14</f>
+        <f t="shared" ref="AK15:AN15" si="59">AK13-AK14</f>
         <v>1211242</v>
       </c>
       <c r="AL15" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="59"/>
         <v>1867916</v>
       </c>
       <c r="AM15" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="59"/>
         <v>2761395</v>
       </c>
       <c r="AN15" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="59"/>
         <v>5116228</v>
       </c>
       <c r="AO15" s="2">
-        <f t="shared" ref="AC15:AQ15" si="35">AO13+AO14</f>
+        <f t="shared" ref="AO15:AQ15" si="60">AO13+AO14</f>
         <v>4491924</v>
       </c>
       <c r="AP15" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="60"/>
         <v>5407990</v>
       </c>
       <c r="AQ15" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="60"/>
         <v>8711631</v>
       </c>
       <c r="AR15" s="2">
         <f>AR13+AR14</f>
         <v>10981201</v>
       </c>
-    </row>
-    <row r="16" spans="2:114" x14ac:dyDescent="0.15">
+      <c r="AS15" s="2">
+        <f t="shared" ref="AS15" si="61">AS13-AS14</f>
+        <v>16473686.709999999</v>
+      </c>
+      <c r="AT15" s="2">
+        <f t="shared" ref="AT15:BC15" si="62">AT13-AT14</f>
+        <v>18278140.871699996</v>
+      </c>
+      <c r="AU15" s="2">
+        <f t="shared" si="62"/>
+        <v>20265729.454508997</v>
+      </c>
+      <c r="AV15" s="2">
+        <f t="shared" si="62"/>
+        <v>22454797.045392934</v>
+      </c>
+      <c r="AW15" s="2">
+        <f t="shared" si="62"/>
+        <v>24865522.181149229</v>
+      </c>
+      <c r="AX15" s="2">
+        <f t="shared" si="62"/>
+        <v>27520100.676624574</v>
+      </c>
+      <c r="AY15" s="2">
+        <f t="shared" si="62"/>
+        <v>30442947.281589698</v>
+      </c>
+      <c r="AZ15" s="2">
+        <f t="shared" si="62"/>
+        <v>33660917.498912171</v>
+      </c>
+      <c r="BA15" s="2">
+        <f t="shared" si="62"/>
+        <v>37203551.579920679</v>
+      </c>
+      <c r="BB15" s="2">
+        <f t="shared" si="62"/>
+        <v>41103342.914431423</v>
+      </c>
+      <c r="BC15" s="2">
+        <f t="shared" si="62"/>
+        <v>45396033.25464163</v>
+      </c>
+      <c r="BD15" s="2">
+        <f>+BC15*(1+$AT$27)</f>
+        <v>44942072.922095209</v>
+      </c>
+      <c r="BE15" s="2">
+        <f t="shared" ref="BE15:DH15" si="63">+BD15*(1+$AT$27)</f>
+        <v>44492652.19287426</v>
+      </c>
+      <c r="BF15" s="2">
+        <f t="shared" si="63"/>
+        <v>44047725.670945518</v>
+      </c>
+      <c r="BG15" s="2">
+        <f t="shared" si="63"/>
+        <v>43607248.414236061</v>
+      </c>
+      <c r="BH15" s="2">
+        <f t="shared" si="63"/>
+        <v>43171175.930093698</v>
+      </c>
+      <c r="BI15" s="2">
+        <f t="shared" si="63"/>
+        <v>42739464.170792758</v>
+      </c>
+      <c r="BJ15" s="2">
+        <f t="shared" si="63"/>
+        <v>42312069.529084831</v>
+      </c>
+      <c r="BK15" s="2">
+        <f t="shared" si="63"/>
+        <v>41888948.833793983</v>
+      </c>
+      <c r="BL15" s="2">
+        <f t="shared" si="63"/>
+        <v>41470059.345456041</v>
+      </c>
+      <c r="BM15" s="2">
+        <f t="shared" si="63"/>
+        <v>41055358.752001479</v>
+      </c>
+      <c r="BN15" s="2">
+        <f t="shared" si="63"/>
+        <v>40644805.164481461</v>
+      </c>
+      <c r="BO15" s="2">
+        <f t="shared" si="63"/>
+        <v>40238357.112836644</v>
+      </c>
+      <c r="BP15" s="2">
+        <f t="shared" si="63"/>
+        <v>39835973.541708276</v>
+      </c>
+      <c r="BQ15" s="2">
+        <f t="shared" si="63"/>
+        <v>39437613.806291193</v>
+      </c>
+      <c r="BR15" s="2">
+        <f t="shared" si="63"/>
+        <v>39043237.668228284</v>
+      </c>
+      <c r="BS15" s="2">
+        <f t="shared" si="63"/>
+        <v>38652805.291546002</v>
+      </c>
+      <c r="BT15" s="2">
+        <f t="shared" si="63"/>
+        <v>38266277.238630541</v>
+      </c>
+      <c r="BU15" s="2">
+        <f t="shared" si="63"/>
+        <v>37883614.466244236</v>
+      </c>
+      <c r="BV15" s="2">
+        <f t="shared" si="63"/>
+        <v>37504778.321581796</v>
+      </c>
+      <c r="BW15" s="2">
+        <f t="shared" si="63"/>
+        <v>37129730.538365975</v>
+      </c>
+      <c r="BX15" s="2">
+        <f t="shared" si="63"/>
+        <v>36758433.232982315</v>
+      </c>
+      <c r="BY15" s="2">
+        <f t="shared" si="63"/>
+        <v>36390848.900652491</v>
+      </c>
+      <c r="BZ15" s="2">
+        <f t="shared" si="63"/>
+        <v>36026940.411645964</v>
+      </c>
+      <c r="CA15" s="2">
+        <f t="shared" si="63"/>
+        <v>35666671.007529505</v>
+      </c>
+      <c r="CB15" s="2">
+        <f t="shared" si="63"/>
+        <v>35310004.297454208</v>
+      </c>
+      <c r="CC15" s="2">
+        <f t="shared" si="63"/>
+        <v>34956904.254479669</v>
+      </c>
+      <c r="CD15" s="2">
+        <f t="shared" si="63"/>
+        <v>34607335.211934872</v>
+      </c>
+      <c r="CE15" s="2">
+        <f t="shared" si="63"/>
+        <v>34261261.859815523</v>
+      </c>
+      <c r="CF15" s="2">
+        <f t="shared" si="63"/>
+        <v>33918649.241217367</v>
+      </c>
+      <c r="CG15" s="2">
+        <f t="shared" si="63"/>
+        <v>33579462.748805195</v>
+      </c>
+      <c r="CH15" s="2">
+        <f t="shared" si="63"/>
+        <v>33243668.121317144</v>
+      </c>
+      <c r="CI15" s="2">
+        <f t="shared" si="63"/>
+        <v>32911231.440103974</v>
+      </c>
+      <c r="CJ15" s="2">
+        <f t="shared" si="63"/>
+        <v>32582119.125702932</v>
+      </c>
+      <c r="CK15" s="2">
+        <f t="shared" si="63"/>
+        <v>32256297.934445903</v>
+      </c>
+      <c r="CL15" s="2">
+        <f t="shared" si="63"/>
+        <v>31933734.955101442</v>
+      </c>
+      <c r="CM15" s="2">
+        <f t="shared" si="63"/>
+        <v>31614397.605550427</v>
+      </c>
+      <c r="CN15" s="2">
+        <f t="shared" si="63"/>
+        <v>31298253.629494924</v>
+      </c>
+      <c r="CO15" s="2">
+        <f t="shared" si="63"/>
+        <v>30985271.093199976</v>
+      </c>
+      <c r="CP15" s="2">
+        <f t="shared" si="63"/>
+        <v>30675418.382267974</v>
+      </c>
+      <c r="CQ15" s="2">
+        <f t="shared" si="63"/>
+        <v>30368664.198445294</v>
+      </c>
+      <c r="CR15" s="2">
+        <f t="shared" si="63"/>
+        <v>30064977.556460842</v>
+      </c>
+      <c r="CS15" s="2">
+        <f t="shared" si="63"/>
+        <v>29764327.780896235</v>
+      </c>
+      <c r="CT15" s="2">
+        <f t="shared" si="63"/>
+        <v>29466684.503087271</v>
+      </c>
+      <c r="CU15" s="2">
+        <f t="shared" si="63"/>
+        <v>29172017.658056397</v>
+      </c>
+      <c r="CV15" s="2">
+        <f t="shared" si="63"/>
+        <v>28880297.481475834</v>
+      </c>
+      <c r="CW15" s="2">
+        <f t="shared" si="63"/>
+        <v>28591494.506661076</v>
+      </c>
+      <c r="CX15" s="2">
+        <f t="shared" si="63"/>
+        <v>28305579.561594464</v>
+      </c>
+      <c r="CY15" s="2">
+        <f t="shared" si="63"/>
+        <v>28022523.765978519</v>
+      </c>
+      <c r="CZ15" s="2">
+        <f t="shared" si="63"/>
+        <v>27742298.528318733</v>
+      </c>
+      <c r="DA15" s="2">
+        <f t="shared" si="63"/>
+        <v>27464875.543035544</v>
+      </c>
+      <c r="DB15" s="2">
+        <f t="shared" si="63"/>
+        <v>27190226.787605189</v>
+      </c>
+      <c r="DC15" s="2">
+        <f t="shared" si="63"/>
+        <v>26918324.519729137</v>
+      </c>
+      <c r="DD15" s="2">
+        <f t="shared" si="63"/>
+        <v>26649141.274531845</v>
+      </c>
+      <c r="DE15" s="2">
+        <f t="shared" si="63"/>
+        <v>26382649.861786526</v>
+      </c>
+      <c r="DF15" s="2">
+        <f t="shared" si="63"/>
+        <v>26118823.363168661</v>
+      </c>
+      <c r="DG15" s="2">
+        <f t="shared" si="63"/>
+        <v>25857635.129536975</v>
+      </c>
+      <c r="DH15" s="2">
+        <f t="shared" si="63"/>
+        <v>25599058.778241605</v>
+      </c>
+    </row>
+    <row r="16" spans="2:114" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>43</v>
       </c>
@@ -2994,7 +4034,7 @@
       <c r="U16" s="6"/>
       <c r="V16" s="6"/>
     </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>1</v>
       </c>
@@ -3019,7 +4059,7 @@
       <c r="U17" s="6"/>
       <c r="V17" s="6"/>
     </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:55" x14ac:dyDescent="0.2">
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
@@ -3041,7 +4081,7 @@
       <c r="U18" s="6"/>
       <c r="V18" s="6"/>
     </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>44</v>
       </c>
@@ -3057,55 +4097,134 @@
         <v>1.8514607906951142E-2</v>
       </c>
       <c r="K19" s="8">
-        <f t="shared" ref="K19:V19" si="36">K3/G3-1</f>
+        <f t="shared" ref="K19:V19" si="64">K3/G3-1</f>
         <v>3.7334100005757653E-2</v>
       </c>
       <c r="L19" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="64"/>
         <v>2.7246694882813172E-2</v>
       </c>
       <c r="M19" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="64"/>
         <v>7.773289783257753E-2</v>
       </c>
       <c r="N19" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="64"/>
         <v>0.12490644166563825</v>
       </c>
       <c r="O19" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="64"/>
         <v>0.14812676047536821</v>
       </c>
       <c r="P19" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="64"/>
         <v>0.16757769135396394</v>
       </c>
       <c r="Q19" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="64"/>
         <v>0.15020895216250496</v>
       </c>
       <c r="R19" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="64"/>
         <v>0.16004936133117087</v>
       </c>
       <c r="S19" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="64"/>
         <v>0.12511269481475784</v>
       </c>
       <c r="T19" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="64"/>
         <v>0.15899222851858563</v>
       </c>
       <c r="U19" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="64"/>
         <v>0.17156793442000229</v>
       </c>
       <c r="V19" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="64"/>
         <v>0.17608419566734557</v>
       </c>
-    </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.15">
+      <c r="W19" s="8">
+        <f t="shared" ref="W19" si="65">W3/S3-1</f>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="X19" s="8">
+        <f t="shared" ref="X19" si="66">X3/T3-1</f>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="Y19" s="8">
+        <f t="shared" ref="Y19" si="67">Y3/U3-1</f>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="Z19" s="8">
+        <f t="shared" ref="Z19" si="68">Z3/V3-1</f>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AA19" s="8"/>
+      <c r="AB19" s="8"/>
+      <c r="AC19" s="8"/>
+      <c r="AD19" s="8">
+        <f t="shared" ref="AD19:AR19" si="69">AD3/AC3-1</f>
+        <v>0.48179966475926239</v>
+      </c>
+      <c r="AE19" s="8">
+        <f t="shared" si="69"/>
+        <v>0.12628967879380015</v>
+      </c>
+      <c r="AF19" s="8">
+        <f t="shared" si="69"/>
+        <v>0.21203109094828276</v>
+      </c>
+      <c r="AG19" s="8">
+        <f t="shared" si="69"/>
+        <v>0.25833306283006152</v>
+      </c>
+      <c r="AH19" s="8">
+        <f t="shared" si="69"/>
+        <v>0.23159576184233854</v>
+      </c>
+      <c r="AI19" s="8">
+        <f t="shared" si="69"/>
+        <v>0.30255249973043785</v>
+      </c>
+      <c r="AJ19" s="8">
+        <f t="shared" si="69"/>
+        <v>0.32410273785598798</v>
+      </c>
+      <c r="AK19" s="8">
+        <f t="shared" si="69"/>
+        <v>0.35078497180252355</v>
+      </c>
+      <c r="AL19" s="8">
+        <f t="shared" si="69"/>
+        <v>0.27618157667990073</v>
+      </c>
+      <c r="AM19" s="8">
+        <f t="shared" si="69"/>
+        <v>0.24010228588401517</v>
+      </c>
+      <c r="AN19" s="8">
+        <f t="shared" si="69"/>
+        <v>0.18810119484449861</v>
+      </c>
+      <c r="AO19" s="8">
+        <f t="shared" si="69"/>
+        <v>6.45739131769969E-2</v>
+      </c>
+      <c r="AP19" s="8">
+        <f t="shared" si="69"/>
+        <v>6.6668047843545297E-2</v>
+      </c>
+      <c r="AQ19" s="8">
+        <f t="shared" si="69"/>
+        <v>0.15649919994477401</v>
+      </c>
+      <c r="AR19" s="8">
+        <f t="shared" si="69"/>
+        <v>0.15851068919677536</v>
+      </c>
+    </row>
+    <row r="20" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>45</v>
       </c>
@@ -3114,83 +4233,165 @@
         <v>0.4599527144121926</v>
       </c>
       <c r="D20" s="8">
-        <f t="shared" ref="D20:V20" si="37">D5/D3</f>
+        <f t="shared" ref="D20:V20" si="70">D5/D3</f>
         <v>0.45271996139354276</v>
       </c>
       <c r="E20" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="70"/>
         <v>0.43788233448480496</v>
       </c>
       <c r="F20" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="70"/>
         <v>0.32035816916619603</v>
       </c>
       <c r="G20" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="70"/>
         <v>0.45541028350229484</v>
       </c>
       <c r="H20" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="70"/>
         <v>0.41145896917005609</v>
       </c>
       <c r="I20" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="70"/>
         <v>0.39579695591078468</v>
       </c>
       <c r="J20" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="70"/>
         <v>0.3117519711087024</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="70"/>
         <v>0.41142887529417072</v>
       </c>
       <c r="L20" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="70"/>
         <v>0.42918062985591954</v>
       </c>
       <c r="M20" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="70"/>
         <v>0.42273710474347631</v>
       </c>
       <c r="N20" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="70"/>
         <v>0.39911806245453746</v>
       </c>
       <c r="O20" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="70"/>
         <v>0.46885386385271127</v>
       </c>
       <c r="P20" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="70"/>
         <v>0.45873258634775943</v>
       </c>
       <c r="Q20" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="70"/>
         <v>0.47887646069301026</v>
       </c>
       <c r="R20" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="70"/>
         <v>0.43713885884885911</v>
       </c>
       <c r="S20" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="70"/>
         <v>0.50078285647239285</v>
       </c>
       <c r="T20" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="70"/>
         <v>0.51934008390162223</v>
       </c>
       <c r="U20" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="70"/>
         <v>0.46445824598770474</v>
       </c>
       <c r="V20" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="70"/>
         <v>0.45873787898225854</v>
       </c>
-    </row>
-    <row r="21" spans="2:22" x14ac:dyDescent="0.15">
+      <c r="W20" s="8">
+        <f t="shared" ref="W20:AR20" si="71">W5/W3</f>
+        <v>0.50078285647239296</v>
+      </c>
+      <c r="X20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.51934008390162223</v>
+      </c>
+      <c r="Y20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.46445824598770474</v>
+      </c>
+      <c r="Z20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.45873787898225854</v>
+      </c>
+      <c r="AA20" s="8"/>
+      <c r="AB20" s="8"/>
+      <c r="AC20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.3723576671868678</v>
+      </c>
+      <c r="AD20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.36344141520082057</v>
+      </c>
+      <c r="AE20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.27246859624712061</v>
+      </c>
+      <c r="AF20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.28742511821754957</v>
+      </c>
+      <c r="AG20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.31825712633087333</v>
+      </c>
+      <c r="AH20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.32274230398033132</v>
+      </c>
+      <c r="AI20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.29139434396193536</v>
+      </c>
+      <c r="AJ20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.31299092007132989</v>
+      </c>
+      <c r="AK20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.36891713304151152</v>
+      </c>
+      <c r="AL20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.38281717010939476</v>
+      </c>
+      <c r="AM20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.38885082510616875</v>
+      </c>
+      <c r="AN20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.41636561226464791</v>
+      </c>
+      <c r="AO20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.39370705238403253</v>
+      </c>
+      <c r="AP20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.41537839553469519</v>
+      </c>
+      <c r="AQ20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.46056556650417324</v>
+      </c>
+      <c r="AR20" s="8">
+        <f t="shared" si="71"/>
+        <v>0.48486575802475956</v>
+      </c>
+    </row>
+    <row r="21" spans="2:55" x14ac:dyDescent="0.2">
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
@@ -3212,7 +4413,7 @@
       <c r="U21" s="6"/>
       <c r="V21" s="6"/>
     </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:55" x14ac:dyDescent="0.2">
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -3234,92 +4435,139 @@
       <c r="U22" s="6"/>
       <c r="V22" s="6"/>
     </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C23" s="6">
-        <f t="shared" ref="C23" si="38">C24-C36</f>
+        <f t="shared" ref="C23" si="72">C24-C36</f>
         <v>-7155635</v>
       </c>
       <c r="D23" s="6">
-        <f t="shared" ref="D23" si="39">D24-D36</f>
+        <f t="shared" ref="D23" si="73">D24-D36</f>
         <v>-7848487</v>
       </c>
       <c r="E23" s="6">
-        <f t="shared" ref="E23" si="40">E24-E36</f>
+        <f t="shared" ref="E23" si="74">E24-E36</f>
         <v>-7155635</v>
       </c>
       <c r="F23" s="6">
-        <f t="shared" ref="F23:G23" si="41">F24-F36</f>
+        <f t="shared" ref="F23:G23" si="75">F24-F36</f>
         <v>-9365046</v>
       </c>
       <c r="G23" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="75"/>
         <v>-8525615</v>
       </c>
       <c r="H23" s="6">
-        <f t="shared" ref="H23" si="42">H24-H36</f>
+        <f t="shared" ref="H23" si="76">H24-H36</f>
         <v>-8413854</v>
       </c>
       <c r="I23" s="6">
-        <f t="shared" ref="I23:J23" si="43">I24-I36</f>
+        <f t="shared" ref="I23:J23" si="77">I24-I36</f>
         <v>-7774384</v>
       </c>
       <c r="J23" s="6">
-        <f t="shared" si="43"/>
+        <f t="shared" si="77"/>
         <v>-8294624</v>
       </c>
       <c r="K23" s="6">
-        <f t="shared" ref="K23:M23" si="44">K24-K36</f>
+        <f t="shared" ref="K23:M23" si="78">K24-K36</f>
         <v>-6609624</v>
       </c>
       <c r="L23" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="78"/>
         <v>-5892549</v>
       </c>
       <c r="M23" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="78"/>
         <v>-6432922</v>
       </c>
       <c r="N23" s="6">
-        <f>N24-N36</f>
+        <f t="shared" ref="N23:V23" si="79">N24-N36</f>
         <v>-7405375</v>
       </c>
       <c r="O23" s="6">
-        <f>O24-O36</f>
+        <f t="shared" si="79"/>
         <v>-6970235</v>
       </c>
       <c r="P23" s="6">
-        <f>P24-P36</f>
+        <f t="shared" si="79"/>
         <v>-7324153</v>
       </c>
       <c r="Q23" s="6">
-        <f>Q24-Q36</f>
+        <f t="shared" si="79"/>
         <v>-6757401</v>
       </c>
       <c r="R23" s="6">
-        <f>R24-R36</f>
+        <f t="shared" si="79"/>
         <v>-5999065</v>
       </c>
       <c r="S23" s="6">
-        <f>S24-S36</f>
+        <f t="shared" si="79"/>
         <v>-6645928</v>
       </c>
       <c r="T23" s="6">
-        <f>T24-T36</f>
+        <f t="shared" si="79"/>
         <v>-6062686</v>
       </c>
       <c r="U23" s="6">
-        <f>U24-U36</f>
+        <f t="shared" si="79"/>
         <v>-5138628</v>
       </c>
       <c r="V23" s="6">
-        <f>V24-V36</f>
+        <f t="shared" si="79"/>
         <v>-5400477</v>
       </c>
-    </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.15">
+      <c r="AR23" s="6">
+        <v>-5400477</v>
+      </c>
+      <c r="AS23" s="2">
+        <f>AR23+AS15</f>
+        <v>11073209.709999999</v>
+      </c>
+      <c r="AT23" s="2">
+        <f t="shared" ref="AT23:BC23" si="80">AS23+AT15</f>
+        <v>29351350.581699997</v>
+      </c>
+      <c r="AU23" s="2">
+        <f t="shared" si="80"/>
+        <v>49617080.036208995</v>
+      </c>
+      <c r="AV23" s="2">
+        <f t="shared" si="80"/>
+        <v>72071877.081601933</v>
+      </c>
+      <c r="AW23" s="2">
+        <f t="shared" si="80"/>
+        <v>96937399.262751162</v>
+      </c>
+      <c r="AX23" s="2">
+        <f t="shared" si="80"/>
+        <v>124457499.93937573</v>
+      </c>
+      <c r="AY23" s="2">
+        <f t="shared" si="80"/>
+        <v>154900447.22096542</v>
+      </c>
+      <c r="AZ23" s="2">
+        <f t="shared" si="80"/>
+        <v>188561364.7198776</v>
+      </c>
+      <c r="BA23" s="2">
+        <f t="shared" si="80"/>
+        <v>225764916.29979828</v>
+      </c>
+      <c r="BB23" s="2">
+        <f t="shared" si="80"/>
+        <v>266868259.2142297</v>
+      </c>
+      <c r="BC23" s="2">
+        <f t="shared" si="80"/>
+        <v>312264292.46887136</v>
+      </c>
+    </row>
+    <row r="24" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>3</v>
       </c>
@@ -3400,7 +4648,7 @@
         <v>9062359</v>
       </c>
     </row>
-    <row r="25" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>60</v>
       </c>
@@ -3464,8 +4712,15 @@
       <c r="V25" s="6">
         <v>3957832</v>
       </c>
-    </row>
-    <row r="26" spans="2:22" x14ac:dyDescent="0.15">
+      <c r="AS25" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AT25" s="13">
+        <f>NPV(AT26,AS15:DH15)</f>
+        <v>403513361.92858946</v>
+      </c>
+    </row>
+    <row r="26" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>47</v>
       </c>
@@ -3529,8 +4784,14 @@
       <c r="V26" s="6">
         <v>32778392</v>
       </c>
-    </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.15">
+      <c r="AS26" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT26" s="12">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="27" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>48</v>
       </c>
@@ -3594,8 +4855,14 @@
       <c r="V27" s="6">
         <v>2004350</v>
       </c>
-    </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.15">
+      <c r="AS27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AT27" s="12">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="28" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>49</v>
       </c>
@@ -3659,8 +4926,14 @@
       <c r="V28" s="6">
         <v>7794060</v>
       </c>
-    </row>
-    <row r="29" spans="2:22" x14ac:dyDescent="0.15">
+      <c r="AS28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AT28" s="12">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="29" spans="2:55" x14ac:dyDescent="0.2">
       <c r="C29" s="9"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
@@ -3681,93 +4954,107 @@
       <c r="T29" s="6"/>
       <c r="U29" s="6"/>
       <c r="V29" s="6"/>
-    </row>
-    <row r="30" spans="2:22" x14ac:dyDescent="0.15">
+      <c r="AS29" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AT29" s="2">
+        <f>AT25/Main!K4</f>
+        <v>95.570317275507065</v>
+      </c>
+    </row>
+    <row r="30" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C30" s="6">
-        <f t="shared" ref="C30:E30" si="45">SUM(C24:C28)</f>
+        <f t="shared" ref="C30:E30" si="81">SUM(C24:C28)</f>
         <v>40123014</v>
       </c>
       <c r="D30" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="81"/>
         <v>40970969</v>
       </c>
       <c r="E30" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="81"/>
         <v>40123014</v>
       </c>
       <c r="F30" s="6">
-        <f t="shared" ref="F30" si="46">SUM(F24:F28)</f>
+        <f t="shared" ref="F30" si="82">SUM(F24:F28)</f>
         <v>44584663</v>
       </c>
       <c r="G30" s="6">
-        <f t="shared" ref="G30:J30" si="47">SUM(G24:G28)</f>
+        <f t="shared" ref="G30:J30" si="83">SUM(G24:G28)</f>
         <v>45330904</v>
       </c>
       <c r="H30" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="83"/>
         <v>46350935</v>
       </c>
       <c r="I30" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="83"/>
         <v>47562187</v>
       </c>
       <c r="J30" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="83"/>
         <v>48594768</v>
       </c>
       <c r="K30" s="6">
-        <f t="shared" ref="K30:M30" si="48">SUM(K24:K28)</f>
+        <f t="shared" ref="K30:M30" si="84">SUM(K24:K28)</f>
         <v>49490345</v>
       </c>
       <c r="L30" s="6">
-        <f t="shared" si="48"/>
+        <f t="shared" si="84"/>
         <v>50817473</v>
       </c>
       <c r="M30" s="6">
-        <f t="shared" si="48"/>
+        <f t="shared" si="84"/>
         <v>49501786</v>
       </c>
       <c r="N30" s="6">
-        <f>SUM(N24:N28)</f>
+        <f t="shared" ref="N30:V30" si="85">SUM(N24:N28)</f>
         <v>48731992</v>
       </c>
       <c r="O30" s="6">
-        <f>SUM(O24:O28)</f>
+        <f t="shared" si="85"/>
         <v>48827721</v>
       </c>
       <c r="P30" s="6">
-        <f>SUM(P24:P28)</f>
+        <f t="shared" si="85"/>
         <v>49098895</v>
       </c>
       <c r="Q30" s="6">
-        <f>SUM(Q24:Q28)</f>
+        <f t="shared" si="85"/>
         <v>52281844</v>
       </c>
       <c r="R30" s="6">
-        <f>SUM(R24:R28)</f>
+        <f t="shared" si="85"/>
         <v>53630374</v>
       </c>
       <c r="S30" s="6">
-        <f>SUM(S24:S28)</f>
+        <f t="shared" si="85"/>
         <v>52087644</v>
       </c>
       <c r="T30" s="6">
-        <f>SUM(T24:T28)</f>
+        <f t="shared" si="85"/>
         <v>53099664</v>
       </c>
       <c r="U30" s="6">
-        <f>SUM(U24:U28)</f>
+        <f t="shared" si="85"/>
         <v>54934835</v>
       </c>
       <c r="V30" s="6">
-        <f>SUM(V24:V28)</f>
+        <f t="shared" si="85"/>
         <v>55596993</v>
       </c>
-    </row>
-    <row r="31" spans="2:22" x14ac:dyDescent="0.15">
+      <c r="AS30" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="AT30" s="14">
+        <f>AT29/Main!K3-1</f>
+        <v>0.24117295162996188</v>
+      </c>
+    </row>
+    <row r="31" spans="2:55" x14ac:dyDescent="0.2">
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
@@ -3789,7 +5076,7 @@
       <c r="U31" s="6"/>
       <c r="V31" s="6"/>
     </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>51</v>
       </c>
@@ -3854,7 +5141,7 @@
         <v>4084854</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
         <v>52</v>
       </c>
@@ -3919,7 +5206,7 @@
         <v>900612</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
         <v>53</v>
       </c>
@@ -3984,7 +5271,7 @@
         <v>3220869</v>
       </c>
     </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>54</v>
       </c>
@@ -4049,7 +5336,7 @@
         <v>1775730</v>
       </c>
     </row>
-    <row r="36" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
         <v>4</v>
       </c>
@@ -4128,7 +5415,7 @@
         <v>14462836</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
         <v>55</v>
       </c>
@@ -4194,7 +5481,7 @@
         <v>1579476</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
         <v>56</v>
       </c>
@@ -4259,7 +5546,7 @@
         <v>2957128</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
@@ -4281,92 +5568,92 @@
       <c r="U39" s="6"/>
       <c r="V39" s="6"/>
     </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C40" s="6">
-        <f t="shared" ref="C40:E40" si="49">SUM(C32:C38)</f>
+        <f t="shared" ref="C40:E40" si="86">SUM(C32:C38)</f>
         <v>27238934</v>
       </c>
       <c r="D40" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="86"/>
         <v>27107098</v>
       </c>
       <c r="E40" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="86"/>
         <v>27238934</v>
       </c>
       <c r="F40" s="6">
-        <f t="shared" ref="F40" si="50">SUM(F32:F38)</f>
+        <f t="shared" ref="F40" si="87">SUM(F32:F38)</f>
         <v>28735370</v>
       </c>
       <c r="G40" s="6">
-        <f t="shared" ref="G40:J40" si="51">SUM(G32:G38)</f>
+        <f t="shared" ref="G40:J40" si="88">SUM(G32:G38)</f>
         <v>27786865</v>
       </c>
       <c r="H40" s="6">
-        <f t="shared" si="51"/>
+        <f t="shared" si="88"/>
         <v>27274961</v>
       </c>
       <c r="I40" s="6">
-        <f t="shared" si="51"/>
+        <f t="shared" si="88"/>
         <v>27034046</v>
       </c>
       <c r="J40" s="6">
-        <f t="shared" si="51"/>
+        <f t="shared" si="88"/>
         <v>27817367</v>
       </c>
       <c r="K40" s="6">
-        <f t="shared" ref="K40:M40" si="52">SUM(K32:K38)</f>
+        <f t="shared" ref="K40:M40" si="89">SUM(K32:K38)</f>
         <v>27662149</v>
       </c>
       <c r="L40" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="89"/>
         <v>27985258</v>
       </c>
       <c r="M40" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="89"/>
         <v>27394159</v>
       </c>
       <c r="N40" s="6">
-        <f>SUM(N32:N38)</f>
+        <f t="shared" ref="N40:V40" si="90">SUM(N32:N38)</f>
         <v>28143679</v>
       </c>
       <c r="O40" s="6">
-        <f>SUM(O32:O38)</f>
+        <f t="shared" si="90"/>
         <v>27462311</v>
       </c>
       <c r="P40" s="6">
-        <f>SUM(P32:P38)</f>
+        <f t="shared" si="90"/>
         <v>26987202</v>
       </c>
       <c r="Q40" s="6">
-        <f>SUM(Q32:Q38)</f>
+        <f t="shared" si="90"/>
         <v>29561108</v>
       </c>
       <c r="R40" s="6">
-        <f>SUM(R32:R38)</f>
+        <f t="shared" si="90"/>
         <v>28886807</v>
       </c>
       <c r="S40" s="6">
-        <f>SUM(S32:S38)</f>
+        <f t="shared" si="90"/>
         <v>28059571</v>
       </c>
       <c r="T40" s="6">
-        <f>SUM(T32:T38)</f>
+        <f t="shared" si="90"/>
         <v>28147747</v>
       </c>
       <c r="U40" s="6">
-        <f>SUM(U32:U38)</f>
+        <f t="shared" si="90"/>
         <v>28980800</v>
       </c>
       <c r="V40" s="6">
-        <f>SUM(V32:V38)</f>
+        <f t="shared" si="90"/>
         <v>28981505</v>
       </c>
     </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
@@ -4388,7 +5675,7 @@
       <c r="U41" s="6"/>
       <c r="V41" s="6"/>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
         <v>59</v>
       </c>
@@ -4453,92 +5740,92 @@
         <v>26615488</v>
       </c>
     </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C43" s="6">
-        <f t="shared" ref="C43" si="53">C42+C40</f>
+        <f t="shared" ref="C43" si="91">C42+C40</f>
         <v>40123014</v>
       </c>
       <c r="D43" s="6">
-        <f t="shared" ref="D43" si="54">D42+D40</f>
+        <f t="shared" ref="D43" si="92">D42+D40</f>
         <v>40970969</v>
       </c>
       <c r="E43" s="6">
-        <f t="shared" ref="E43" si="55">E42+E40</f>
+        <f t="shared" ref="E43" si="93">E42+E40</f>
         <v>40123014</v>
       </c>
       <c r="F43" s="6">
-        <f t="shared" ref="F43:G43" si="56">F42+F40</f>
+        <f t="shared" ref="F43:G43" si="94">F42+F40</f>
         <v>44584618</v>
       </c>
       <c r="G43" s="6">
-        <f t="shared" si="56"/>
+        <f t="shared" si="94"/>
         <v>45330904</v>
       </c>
       <c r="H43" s="6">
-        <f t="shared" ref="H43" si="57">H42+H40</f>
+        <f t="shared" ref="H43" si="95">H42+H40</f>
         <v>46350935</v>
       </c>
       <c r="I43" s="6">
-        <f t="shared" ref="I43:J43" si="58">I42+I40</f>
+        <f t="shared" ref="I43:J43" si="96">I42+I40</f>
         <v>47562187</v>
       </c>
       <c r="J43" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="96"/>
         <v>48594768</v>
       </c>
       <c r="K43" s="6">
-        <f t="shared" ref="K43:M43" si="59">K42+K40</f>
+        <f t="shared" ref="K43:M43" si="97">K42+K40</f>
         <v>49490345</v>
       </c>
       <c r="L43" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="97"/>
         <v>50817473</v>
       </c>
       <c r="M43" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="97"/>
         <v>49501786</v>
       </c>
       <c r="N43" s="6">
-        <f>N42+N40</f>
+        <f t="shared" ref="N43:V43" si="98">N42+N40</f>
         <v>48731992</v>
       </c>
       <c r="O43" s="6">
-        <f>O42+O40</f>
+        <f t="shared" si="98"/>
         <v>48827721</v>
       </c>
       <c r="P43" s="6">
-        <f>P42+P40</f>
+        <f t="shared" si="98"/>
         <v>49099895</v>
       </c>
       <c r="Q43" s="6">
-        <f>Q42+Q40</f>
+        <f t="shared" si="98"/>
         <v>52281844</v>
       </c>
       <c r="R43" s="6">
-        <f>R42+R40</f>
+        <f t="shared" si="98"/>
         <v>53630374</v>
       </c>
       <c r="S43" s="6">
-        <f>S42+S40</f>
+        <f t="shared" si="98"/>
         <v>52087644</v>
       </c>
       <c r="T43" s="6">
-        <f>T42+T40</f>
+        <f t="shared" si="98"/>
         <v>53099646</v>
       </c>
       <c r="U43" s="6">
-        <f>U42+U40</f>
+        <f t="shared" si="98"/>
         <v>54934835</v>
       </c>
       <c r="V43" s="6">
-        <f>V42+V40</f>
+        <f t="shared" si="98"/>
         <v>55596993</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
@@ -4560,52 +5847,52 @@
       <c r="U44" s="6"/>
       <c r="V44" s="6"/>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C45" s="6">
-        <f t="shared" ref="C45:T45" si="60">C15</f>
+        <f t="shared" ref="C45:T45" si="99">C15</f>
         <v>1706715</v>
       </c>
       <c r="D45" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="99"/>
         <v>1353013</v>
       </c>
       <c r="E45" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="99"/>
         <v>1449071</v>
       </c>
       <c r="F45" s="6">
-        <f t="shared" ref="F45" si="61">F15</f>
+        <f t="shared" ref="F45" si="100">F15</f>
         <v>607429</v>
       </c>
       <c r="G45" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="99"/>
         <v>1597447</v>
       </c>
       <c r="H45" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="99"/>
         <v>1440951</v>
       </c>
       <c r="I45" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="99"/>
         <v>1398242</v>
       </c>
       <c r="J45" s="6">
-        <f t="shared" ref="J45" si="62">J15</f>
+        <f t="shared" ref="J45" si="101">J15</f>
         <v>55284</v>
       </c>
       <c r="K45" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="99"/>
         <v>1305120</v>
       </c>
       <c r="L45" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="99"/>
         <v>1487610</v>
       </c>
       <c r="M45" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="99"/>
         <v>1677422</v>
       </c>
       <c r="N45" s="6">
@@ -4613,15 +5900,15 @@
         <v>937838</v>
       </c>
       <c r="O45" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="99"/>
         <v>2332209</v>
       </c>
       <c r="P45" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="99"/>
         <v>2147306</v>
       </c>
       <c r="Q45" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="99"/>
         <v>2363509</v>
       </c>
       <c r="R45" s="6">
@@ -4629,11 +5916,11 @@
         <v>1868607</v>
       </c>
       <c r="S45" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="99"/>
         <v>2890351</v>
       </c>
       <c r="T45" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="99"/>
         <v>3125413</v>
       </c>
       <c r="U45" s="6">
@@ -4645,7 +5932,7 @@
         <v>2418521</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
         <v>62</v>
       </c>
@@ -4713,7 +6000,7 @@
         <v>2418521</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
         <v>65</v>
       </c>
@@ -4778,7 +6065,7 @@
         <v>-5057212</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B48" s="2" t="s">
         <v>66</v>
       </c>
@@ -4843,7 +6130,7 @@
         <v>-9795</v>
       </c>
     </row>
-    <row r="49" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
         <v>67</v>
       </c>
@@ -4908,7 +6195,7 @@
         <v>4764236</v>
       </c>
     </row>
-    <row r="50" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
         <v>63</v>
       </c>
@@ -4973,7 +6260,7 @@
         <v>85983</v>
       </c>
     </row>
-    <row r="51" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
         <v>64</v>
       </c>
@@ -5038,7 +6325,7 @@
         <v>134624</v>
       </c>
     </row>
-    <row r="52" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
         <v>68</v>
       </c>
@@ -5103,7 +6390,7 @@
         <v>-9730</v>
       </c>
     </row>
-    <row r="53" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B53" s="2" t="s">
         <v>69</v>
       </c>
@@ -5168,7 +6455,7 @@
         <v>200289</v>
       </c>
     </row>
-    <row r="54" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B54" s="2" t="s">
         <v>70</v>
       </c>
@@ -5233,7 +6520,7 @@
         <v>-162912</v>
       </c>
     </row>
-    <row r="55" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B55" s="2" t="s">
         <v>71</v>
       </c>
@@ -5298,7 +6585,7 @@
         <v>-313014</v>
       </c>
     </row>
-    <row r="56" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B56" s="2" t="s">
         <v>72</v>
       </c>
@@ -5363,7 +6650,7 @@
         <v>117890</v>
       </c>
     </row>
-    <row r="57" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B57" s="2" t="s">
         <v>73</v>
       </c>
@@ -5428,7 +6715,7 @@
         <v>134889</v>
       </c>
     </row>
-    <row r="58" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B58" s="2" t="s">
         <v>74</v>
       </c>
@@ -5493,7 +6780,7 @@
         <v>51055</v>
       </c>
     </row>
-    <row r="59" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B59" s="2" t="s">
         <v>75</v>
       </c>
@@ -5558,92 +6845,92 @@
         <v>-243182</v>
       </c>
     </row>
-    <row r="60" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B60" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C60" s="6">
-        <f>SUM(C46:C59)</f>
+        <f t="shared" ref="C60:V60" si="102">SUM(C46:C59)</f>
         <v>777266</v>
       </c>
       <c r="D60" s="6">
-        <f>SUM(D46:D59)</f>
+        <f t="shared" si="102"/>
         <v>-63761</v>
       </c>
       <c r="E60" s="6">
-        <f>SUM(E46:E59)</f>
+        <f t="shared" si="102"/>
         <v>82379</v>
       </c>
       <c r="F60" s="6">
-        <f>SUM(F46:F59)</f>
+        <f t="shared" si="102"/>
         <v>-403274</v>
       </c>
       <c r="G60" s="6">
-        <f>SUM(G46:G59)</f>
+        <f t="shared" si="102"/>
         <v>922839</v>
       </c>
       <c r="H60" s="6">
-        <f>SUM(H46:H59)</f>
+        <f t="shared" si="102"/>
         <v>102750</v>
       </c>
       <c r="I60" s="6">
-        <f>SUM(I46:I59)</f>
+        <f t="shared" si="102"/>
         <v>556810</v>
       </c>
       <c r="J60" s="6">
-        <f>SUM(J46:J59)</f>
+        <f t="shared" si="102"/>
         <v>443758</v>
       </c>
       <c r="K60" s="6">
-        <f>SUM(K46:K59)</f>
+        <f t="shared" si="102"/>
         <v>2178740</v>
       </c>
       <c r="L60" s="6">
-        <f>SUM(L46:L59)</f>
+        <f t="shared" si="102"/>
         <v>1440232</v>
       </c>
       <c r="M60" s="6">
-        <f>SUM(M46:M59)</f>
+        <f t="shared" si="102"/>
         <v>1992315</v>
       </c>
       <c r="N60" s="6">
-        <f>SUM(N46:N59)</f>
+        <f t="shared" si="102"/>
         <v>1663014</v>
       </c>
       <c r="O60" s="6">
-        <f>SUM(O46:O59)</f>
+        <f t="shared" si="102"/>
         <v>2212522</v>
       </c>
       <c r="P60" s="6">
-        <f>SUM(P46:P59)</f>
+        <f t="shared" si="102"/>
         <v>1290847</v>
       </c>
       <c r="Q60" s="6">
-        <f>SUM(Q46:Q59)</f>
+        <f t="shared" si="102"/>
         <v>2321101</v>
       </c>
       <c r="R60" s="6">
-        <f>SUM(R46:R59)</f>
+        <f t="shared" si="102"/>
         <v>1536894</v>
       </c>
       <c r="S60" s="6">
-        <f>SUM(S46:S59)</f>
+        <f t="shared" si="102"/>
         <v>2789199</v>
       </c>
       <c r="T60" s="6">
-        <f>SUM(T46:T59)</f>
+        <f t="shared" si="102"/>
         <v>2423258</v>
       </c>
       <c r="U60" s="6">
-        <f>SUM(U46:U59)</f>
+        <f t="shared" si="102"/>
         <v>2825174</v>
       </c>
       <c r="V60" s="6">
-        <f>SUM(V46:V59)</f>
+        <f t="shared" si="102"/>
         <v>2111642</v>
       </c>
     </row>
-    <row r="61" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
@@ -5665,7 +6952,7 @@
       <c r="U61" s="6"/>
       <c r="V61" s="6"/>
     </row>
-    <row r="62" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B62" s="2" t="s">
         <v>77</v>
       </c>
@@ -5730,7 +7017,7 @@
         <v>-239335</v>
       </c>
     </row>
-    <row r="63" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B63" s="2" t="s">
         <v>83</v>
       </c>
@@ -5795,7 +7082,7 @@
         <v>-17194</v>
       </c>
     </row>
-    <row r="64" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B64" s="2" t="s">
         <v>84</v>
       </c>
@@ -5860,7 +7147,7 @@
         <v>-8450</v>
       </c>
     </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B65" s="2" t="s">
         <v>85</v>
       </c>
@@ -5925,92 +7212,92 @@
         <v>8450</v>
       </c>
     </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B66" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C66" s="6">
-        <f>SUM(C62:C65)</f>
+        <f t="shared" ref="C66:V66" si="103">SUM(C62:C65)</f>
         <v>-85616</v>
       </c>
       <c r="D66" s="6">
-        <f>SUM(D62:D65)</f>
+        <f t="shared" si="103"/>
         <v>-111278</v>
       </c>
       <c r="E66" s="6">
-        <f>SUM(E62:E65)</f>
+        <f t="shared" si="103"/>
         <v>-188631</v>
       </c>
       <c r="F66" s="6">
-        <f>SUM(F62:F65)</f>
+        <f t="shared" si="103"/>
         <v>-954328</v>
       </c>
       <c r="G66" s="6">
-        <f>SUM(G62:G65)</f>
+        <f t="shared" si="103"/>
         <v>-245679</v>
       </c>
       <c r="H66" s="6">
-        <f>SUM(H62:H65)</f>
+        <f t="shared" si="103"/>
         <v>-158894</v>
       </c>
       <c r="I66" s="6">
-        <f>SUM(I62:I65)</f>
+        <f t="shared" si="103"/>
         <v>-84960</v>
       </c>
       <c r="J66" s="6">
-        <f>SUM(J62:J65)</f>
+        <f t="shared" si="103"/>
         <v>-1586859</v>
       </c>
       <c r="K66" s="6">
-        <f>SUM(K62:K65)</f>
+        <f t="shared" si="103"/>
         <v>-263653</v>
       </c>
       <c r="L66" s="6">
-        <f>SUM(L62:L65)</f>
+        <f t="shared" si="103"/>
         <v>97737</v>
       </c>
       <c r="M66" s="6">
-        <f>SUM(M62:M65)</f>
+        <f t="shared" si="103"/>
         <v>296071</v>
       </c>
       <c r="N66" s="6">
-        <f>SUM(N62:N65)</f>
+        <f t="shared" si="103"/>
         <v>411596</v>
       </c>
       <c r="O66" s="6">
-        <f>SUM(O62:O65)</f>
+        <f t="shared" si="103"/>
         <v>-71714</v>
       </c>
       <c r="P66" s="6">
-        <f>SUM(P62:P65)</f>
+        <f t="shared" si="103"/>
         <v>-78287</v>
       </c>
       <c r="Q66" s="6">
-        <f>SUM(Q62:Q65)</f>
+        <f t="shared" si="103"/>
         <v>-1869109</v>
       </c>
       <c r="R66" s="6">
-        <f>SUM(R62:R65)</f>
+        <f t="shared" si="103"/>
         <v>-158674</v>
       </c>
       <c r="S66" s="6">
-        <f>SUM(S62:S65)</f>
+        <f t="shared" si="103"/>
         <v>485662</v>
       </c>
       <c r="T66" s="6">
-        <f>SUM(T62:T65)</f>
+        <f t="shared" si="103"/>
         <v>768684</v>
       </c>
       <c r="U66" s="6">
-        <f>SUM(U62:U65)</f>
+        <f t="shared" si="103"/>
         <v>43871</v>
       </c>
       <c r="V66" s="6">
-        <f>SUM(V62:V65)</f>
+        <f t="shared" si="103"/>
         <v>-256529</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
@@ -6032,7 +7319,7 @@
       <c r="U67" s="6"/>
       <c r="V67" s="6"/>
     </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B68" s="2" t="s">
         <v>86</v>
       </c>
@@ -6097,7 +7384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B69" s="2" t="s">
         <v>79</v>
       </c>
@@ -6162,7 +7449,7 @@
         <v>76082</v>
       </c>
     </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B70" s="2" t="s">
         <v>87</v>
       </c>
@@ -6227,7 +7514,7 @@
         <v>-2079559</v>
       </c>
     </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B71" s="2" t="s">
         <v>88</v>
       </c>
@@ -6292,7 +7579,7 @@
         <v>-5985</v>
       </c>
     </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B72" s="2" t="s">
         <v>89</v>
       </c>
@@ -6357,92 +7644,92 @@
         <v>-67948</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B73" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C73" s="6">
-        <f>SUM(C68:C72)</f>
+        <f t="shared" ref="C73:V73" si="104">SUM(C68:C72)</f>
         <v>-451929</v>
       </c>
       <c r="D73" s="6">
-        <f>SUM(D68:D72)</f>
+        <f t="shared" si="104"/>
         <v>-480273</v>
       </c>
       <c r="E73" s="6">
-        <f>SUM(E68:E72)</f>
+        <f t="shared" si="104"/>
         <v>118445</v>
       </c>
       <c r="F73" s="6">
-        <f>SUM(F68:F72)</f>
+        <f t="shared" si="104"/>
         <v>-136019</v>
       </c>
       <c r="G73" s="6">
-        <f>SUM(G68:G72)</f>
+        <f t="shared" si="104"/>
         <v>-686322</v>
       </c>
       <c r="H73" s="6">
-        <f>SUM(H68:H72)</f>
+        <f t="shared" si="104"/>
         <v>11250</v>
       </c>
       <c r="I73" s="6">
-        <f>SUM(I68:I72)</f>
+        <f t="shared" si="104"/>
         <v>4113</v>
       </c>
       <c r="J73" s="6">
-        <f>SUM(J68:J72)</f>
+        <f t="shared" si="104"/>
         <v>6705</v>
       </c>
       <c r="K73" s="6">
-        <f>SUM(K68:K72)</f>
+        <f t="shared" si="104"/>
         <v>-374073</v>
       </c>
       <c r="L73" s="6">
-        <f>SUM(L68:L72)</f>
+        <f t="shared" si="104"/>
         <v>-649349</v>
       </c>
       <c r="M73" s="6">
-        <f>SUM(M68:M72)</f>
+        <f t="shared" si="104"/>
         <v>-2475108</v>
       </c>
       <c r="N73" s="6">
-        <f>SUM(N68:N72)</f>
+        <f t="shared" si="104"/>
         <v>-2452273</v>
       </c>
       <c r="O73" s="6">
-        <f>SUM(O68:O72)</f>
+        <f t="shared" si="104"/>
         <v>-2132944</v>
       </c>
       <c r="P73" s="6">
-        <f>SUM(P68:P72)</f>
+        <f t="shared" si="104"/>
         <v>-1489381</v>
       </c>
       <c r="Q73" s="6">
-        <f>SUM(Q68:Q72)</f>
+        <f t="shared" si="104"/>
         <v>226596</v>
       </c>
       <c r="R73" s="6">
-        <f>SUM(R68:R72)</f>
+        <f t="shared" si="104"/>
         <v>-678698</v>
       </c>
       <c r="S73" s="6">
-        <f>SUM(S68:S72)</f>
+        <f t="shared" si="104"/>
         <v>-4028316</v>
       </c>
       <c r="T73" s="6">
-        <f>SUM(T68:T72)</f>
+        <f t="shared" si="104"/>
         <v>-2502868</v>
       </c>
       <c r="U73" s="6">
-        <f>SUM(U68:U72)</f>
+        <f t="shared" si="104"/>
         <v>-1737029</v>
       </c>
       <c r="V73" s="6">
-        <f>SUM(V68:V72)</f>
+        <f t="shared" si="104"/>
         <v>-2077410</v>
       </c>
     </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B74" s="2" t="s">
         <v>81</v>
       </c>
@@ -6507,7 +7794,7 @@
         <v>-29377</v>
       </c>
     </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B75" s="2" t="s">
         <v>82</v>
       </c>
@@ -6550,7 +7837,7 @@
         <v>-222297</v>
       </c>
     </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="6"/>
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
@@ -6572,7 +7859,7 @@
       <c r="U76" s="6"/>
       <c r="V76" s="6"/>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B77" s="2" t="s">
         <v>90</v>
       </c>
@@ -6597,7 +7884,7 @@
       <c r="U77" s="6"/>
       <c r="V77" s="6"/>
     </row>
-    <row r="78" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B78" s="2" t="s">
         <v>91</v>
       </c>
@@ -6631,7 +7918,7 @@
         <v>1863857</v>
       </c>
     </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C79" s="6"/>
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
@@ -6653,7 +7940,7 @@
       <c r="U79" s="6"/>
       <c r="V79" s="6"/>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="6"/>
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
@@ -6675,7 +7962,7 @@
       <c r="U80" s="6"/>
       <c r="V80" s="6"/>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="6"/>
       <c r="D81" s="6"/>
       <c r="E81" s="6"/>
@@ -6697,7 +7984,7 @@
       <c r="U81" s="6"/>
       <c r="V81" s="6"/>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="6"/>
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
@@ -6719,7 +8006,7 @@
       <c r="U82" s="6"/>
       <c r="V82" s="6"/>
     </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="6"/>
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
@@ -6741,7 +8028,7 @@
       <c r="U83" s="6"/>
       <c r="V83" s="6"/>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="6"/>
       <c r="D84" s="6"/>
       <c r="E84" s="6"/>
@@ -6763,7 +8050,7 @@
       <c r="U84" s="6"/>
       <c r="V84" s="6"/>
     </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="6"/>
       <c r="D85" s="6"/>
       <c r="E85" s="6"/>
@@ -6785,7 +8072,7 @@
       <c r="U85" s="6"/>
       <c r="V85" s="6"/>
     </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="6"/>
       <c r="D86" s="6"/>
       <c r="E86" s="6"/>
@@ -6807,7 +8094,7 @@
       <c r="U86" s="6"/>
       <c r="V86" s="6"/>
     </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="6"/>
       <c r="D87" s="6"/>
       <c r="E87" s="6"/>
@@ -6829,7 +8116,7 @@
       <c r="U87" s="6"/>
       <c r="V87" s="6"/>
     </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="6"/>
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
@@ -6851,7 +8138,7 @@
       <c r="U88" s="6"/>
       <c r="V88" s="6"/>
     </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="6"/>
       <c r="D89" s="6"/>
       <c r="E89" s="6"/>
@@ -6873,7 +8160,7 @@
       <c r="U89" s="6"/>
       <c r="V89" s="6"/>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="6"/>
       <c r="D90" s="6"/>
       <c r="E90" s="6"/>
@@ -6895,7 +8182,7 @@
       <c r="U90" s="6"/>
       <c r="V90" s="6"/>
     </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="6"/>
       <c r="D91" s="6"/>
       <c r="E91" s="6"/>
@@ -6917,7 +8204,7 @@
       <c r="U91" s="6"/>
       <c r="V91" s="6"/>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="6"/>
       <c r="D92" s="6"/>
       <c r="E92" s="6"/>
@@ -6939,7 +8226,7 @@
       <c r="U92" s="6"/>
       <c r="V92" s="6"/>
     </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="6"/>
       <c r="D93" s="6"/>
       <c r="E93" s="6"/>
@@ -6961,7 +8248,7 @@
       <c r="U93" s="6"/>
       <c r="V93" s="6"/>
     </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="6"/>
       <c r="D94" s="6"/>
       <c r="E94" s="6"/>
@@ -6983,7 +8270,7 @@
       <c r="U94" s="6"/>
       <c r="V94" s="6"/>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="6"/>
       <c r="D95" s="6"/>
       <c r="E95" s="6"/>
@@ -7005,7 +8292,7 @@
       <c r="U95" s="6"/>
       <c r="V95" s="6"/>
     </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="6"/>
       <c r="D96" s="6"/>
       <c r="E96" s="6"/>
@@ -7027,7 +8314,7 @@
       <c r="U96" s="6"/>
       <c r="V96" s="6"/>
     </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="6"/>
       <c r="D97" s="6"/>
       <c r="E97" s="6"/>
@@ -7049,7 +8336,7 @@
       <c r="U97" s="6"/>
       <c r="V97" s="6"/>
     </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="6"/>
       <c r="D98" s="6"/>
       <c r="E98" s="6"/>
@@ -7071,7 +8358,7 @@
       <c r="U98" s="6"/>
       <c r="V98" s="6"/>
     </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="6"/>
       <c r="D99" s="6"/>
       <c r="E99" s="6"/>
@@ -7093,7 +8380,7 @@
       <c r="U99" s="6"/>
       <c r="V99" s="6"/>
     </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="6"/>
       <c r="D100" s="6"/>
       <c r="E100" s="6"/>
@@ -7115,7 +8402,7 @@
       <c r="U100" s="6"/>
       <c r="V100" s="6"/>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="6"/>
       <c r="D101" s="6"/>
       <c r="E101" s="6"/>
@@ -7137,7 +8424,7 @@
       <c r="U101" s="6"/>
       <c r="V101" s="6"/>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="6"/>
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
@@ -7159,7 +8446,7 @@
       <c r="U102" s="6"/>
       <c r="V102" s="6"/>
     </row>
-    <row r="103" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="103" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C103" s="6"/>
       <c r="D103" s="6"/>
       <c r="E103" s="6"/>
@@ -7181,7 +8468,7 @@
       <c r="U103" s="6"/>
       <c r="V103" s="6"/>
     </row>
-    <row r="104" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="104" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C104" s="6"/>
       <c r="D104" s="6"/>
       <c r="E104" s="6"/>
@@ -7203,7 +8490,7 @@
       <c r="U104" s="6"/>
       <c r="V104" s="6"/>
     </row>
-    <row r="105" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C105" s="6"/>
       <c r="D105" s="6"/>
       <c r="E105" s="6"/>
@@ -7225,7 +8512,7 @@
       <c r="U105" s="6"/>
       <c r="V105" s="6"/>
     </row>
-    <row r="106" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="106" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C106" s="6"/>
       <c r="D106" s="6"/>
       <c r="E106" s="6"/>
@@ -7247,7 +8534,7 @@
       <c r="U106" s="6"/>
       <c r="V106" s="6"/>
     </row>
-    <row r="107" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="107" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C107" s="6"/>
       <c r="D107" s="6"/>
       <c r="E107" s="6"/>
@@ -7269,7 +8556,7 @@
       <c r="U107" s="6"/>
       <c r="V107" s="6"/>
     </row>
-    <row r="108" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="108" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C108" s="6"/>
       <c r="D108" s="6"/>
       <c r="E108" s="6"/>
@@ -7291,7 +8578,7 @@
       <c r="U108" s="6"/>
       <c r="V108" s="6"/>
     </row>
-    <row r="109" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="109" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C109" s="6"/>
       <c r="D109" s="6"/>
       <c r="E109" s="6"/>
@@ -7313,7 +8600,7 @@
       <c r="U109" s="6"/>
       <c r="V109" s="6"/>
     </row>
-    <row r="110" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="110" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C110" s="6"/>
       <c r="D110" s="6"/>
       <c r="E110" s="6"/>
@@ -7335,7 +8622,7 @@
       <c r="U110" s="6"/>
       <c r="V110" s="6"/>
     </row>
-    <row r="111" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="111" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C111" s="6"/>
       <c r="D111" s="6"/>
       <c r="E111" s="6"/>
@@ -7357,7 +8644,7 @@
       <c r="U111" s="6"/>
       <c r="V111" s="6"/>
     </row>
-    <row r="112" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="112" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C112" s="6"/>
       <c r="D112" s="6"/>
       <c r="E112" s="6"/>
@@ -7379,7 +8666,7 @@
       <c r="U112" s="6"/>
       <c r="V112" s="6"/>
     </row>
-    <row r="113" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="113" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C113" s="6"/>
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
@@ -7401,7 +8688,7 @@
       <c r="U113" s="6"/>
       <c r="V113" s="6"/>
     </row>
-    <row r="114" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="114" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C114" s="6"/>
       <c r="D114" s="6"/>
       <c r="E114" s="6"/>
@@ -7423,7 +8710,7 @@
       <c r="U114" s="6"/>
       <c r="V114" s="6"/>
     </row>
-    <row r="115" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="115" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C115" s="6"/>
       <c r="D115" s="6"/>
       <c r="E115" s="6"/>
@@ -7445,7 +8732,7 @@
       <c r="U115" s="6"/>
       <c r="V115" s="6"/>
     </row>
-    <row r="116" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="116" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C116" s="6"/>
       <c r="D116" s="6"/>
       <c r="E116" s="6"/>
@@ -7467,7 +8754,7 @@
       <c r="U116" s="6"/>
       <c r="V116" s="6"/>
     </row>
-    <row r="117" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="117" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C117" s="6"/>
       <c r="D117" s="6"/>
       <c r="E117" s="6"/>
@@ -7489,7 +8776,7 @@
       <c r="U117" s="6"/>
       <c r="V117" s="6"/>
     </row>
-    <row r="118" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="118" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C118" s="6"/>
       <c r="D118" s="6"/>
       <c r="E118" s="6"/>
@@ -7511,7 +8798,7 @@
       <c r="U118" s="6"/>
       <c r="V118" s="6"/>
     </row>
-    <row r="119" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="119" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C119" s="6"/>
       <c r="D119" s="6"/>
       <c r="E119" s="6"/>
@@ -7533,7 +8820,7 @@
       <c r="U119" s="6"/>
       <c r="V119" s="6"/>
     </row>
-    <row r="120" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="120" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C120" s="6"/>
       <c r="D120" s="6"/>
       <c r="E120" s="6"/>
@@ -7555,7 +8842,7 @@
       <c r="U120" s="6"/>
       <c r="V120" s="6"/>
     </row>
-    <row r="121" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="121" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C121" s="6"/>
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
@@ -7577,7 +8864,7 @@
       <c r="U121" s="6"/>
       <c r="V121" s="6"/>
     </row>
-    <row r="122" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="122" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C122" s="6"/>
       <c r="D122" s="6"/>
       <c r="E122" s="6"/>
@@ -7599,7 +8886,7 @@
       <c r="U122" s="6"/>
       <c r="V122" s="6"/>
     </row>
-    <row r="123" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="123" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C123" s="6"/>
       <c r="D123" s="6"/>
       <c r="E123" s="6"/>
@@ -7621,7 +8908,7 @@
       <c r="U123" s="6"/>
       <c r="V123" s="6"/>
     </row>
-    <row r="124" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="124" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C124" s="6"/>
       <c r="D124" s="6"/>
       <c r="E124" s="6"/>
@@ -7643,7 +8930,7 @@
       <c r="U124" s="6"/>
       <c r="V124" s="6"/>
     </row>
-    <row r="125" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="125" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C125" s="6"/>
       <c r="D125" s="6"/>
       <c r="E125" s="6"/>
@@ -7665,7 +8952,7 @@
       <c r="U125" s="6"/>
       <c r="V125" s="6"/>
     </row>
-    <row r="126" spans="3:22" x14ac:dyDescent="0.15">
+    <row r="126" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C126" s="6"/>
       <c r="D126" s="6"/>
       <c r="E126" s="6"/>
